--- a/data/excel/kof_barometer_global.xlsx
+++ b/data/excel/kof_barometer_global.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D419"/>
+  <dimension ref="A1:D420"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -396,10 +396,10 @@
         <v>1991-07</v>
       </c>
       <c r="B2">
-        <v>92.7676192195664</v>
+        <v>91.2926185925261</v>
       </c>
       <c r="C2">
-        <v>98.3108858670863</v>
+        <v>101.525391943898</v>
       </c>
     </row>
     <row r="3">
@@ -407,10 +407,10 @@
         <v>1991-08</v>
       </c>
       <c r="B3">
-        <v>96.0749196627955</v>
+        <v>96.1471703427449</v>
       </c>
       <c r="C3">
-        <v>97.6531421886024</v>
+        <v>101.602478409701</v>
       </c>
     </row>
     <row r="4">
@@ -418,10 +418,10 @@
         <v>1991-09</v>
       </c>
       <c r="B4">
-        <v>96.6813707670306</v>
+        <v>96.4104534566082</v>
       </c>
       <c r="C4">
-        <v>95.9674225307474</v>
+        <v>101.889240400541</v>
       </c>
     </row>
     <row r="5">
@@ -429,10 +429,10 @@
         <v>1991-10</v>
       </c>
       <c r="B5">
-        <v>100.971875911587</v>
+        <v>100.863275340246</v>
       </c>
       <c r="C5">
-        <v>99.3928610420562</v>
+        <v>103.592944723927</v>
       </c>
       <c r="D5">
         <v>1.00333405280644</v>
@@ -443,10 +443,10 @@
         <v>1991-11</v>
       </c>
       <c r="B6">
-        <v>99.4459454900413</v>
+        <v>99.5945388652616</v>
       </c>
       <c r="C6">
-        <v>99.7804388650601</v>
+        <v>101.800618314923</v>
       </c>
       <c r="D6">
         <v>1.19175407265337</v>
@@ -457,10 +457,10 @@
         <v>1991-12</v>
       </c>
       <c r="B7">
-        <v>99.4330203531992</v>
+        <v>99.9172087254227</v>
       </c>
       <c r="C7">
-        <v>100.570942675095</v>
+        <v>102.468663348061</v>
       </c>
       <c r="D7">
         <v>1.37842864990809</v>
@@ -471,10 +471,10 @@
         <v>1992-01</v>
       </c>
       <c r="B8">
-        <v>101.559631542116</v>
+        <v>102.000644121797</v>
       </c>
       <c r="C8">
-        <v>97.6218997313537</v>
+        <v>100.668769687218</v>
       </c>
       <c r="D8">
         <v>1.56335316378625</v>
@@ -485,10 +485,10 @@
         <v>1992-02</v>
       </c>
       <c r="B9">
-        <v>100.051344924781</v>
+        <v>99.7660455400943</v>
       </c>
       <c r="C9">
-        <v>98.3122655177895</v>
+        <v>102.188566813241</v>
       </c>
       <c r="D9">
         <v>1.64538453920532</v>
@@ -499,10 +499,10 @@
         <v>1992-03</v>
       </c>
       <c r="B10">
-        <v>98.4001653112769</v>
+        <v>98.6480974847466</v>
       </c>
       <c r="C10">
-        <v>102.493847874513</v>
+        <v>103.637696317077</v>
       </c>
       <c r="D10">
         <v>1.62457067794716</v>
@@ -513,10 +513,10 @@
         <v>1992-04</v>
       </c>
       <c r="B11">
-        <v>96.7832803414072</v>
+        <v>98.1826059246127</v>
       </c>
       <c r="C11">
-        <v>101.998547756535</v>
+        <v>106.114932590637</v>
       </c>
       <c r="D11">
         <v>1.50135420016042</v>
@@ -527,10 +527,10 @@
         <v>1992-05</v>
       </c>
       <c r="B12">
-        <v>96.6617739987262</v>
+        <v>95.7016858839195</v>
       </c>
       <c r="C12">
-        <v>101.887201445708</v>
+        <v>105.673855115573</v>
       </c>
       <c r="D12">
         <v>1.47788188112837</v>
@@ -541,10 +541,10 @@
         <v>1992-06</v>
       </c>
       <c r="B13">
-        <v>96.4185124448516</v>
+        <v>95.31366152935</v>
       </c>
       <c r="C13">
-        <v>100.367558901795</v>
+        <v>105.049894279889</v>
       </c>
       <c r="D13">
         <v>1.55371345566022</v>
@@ -555,10 +555,10 @@
         <v>1992-07</v>
       </c>
       <c r="B14">
-        <v>96.0623995510879</v>
+        <v>95.4641441190347</v>
       </c>
       <c r="C14">
-        <v>103.208746393782</v>
+        <v>104.835862312315</v>
       </c>
       <c r="D14">
         <v>1.72877644391514</v>
@@ -569,10 +569,10 @@
         <v>1992-08</v>
       </c>
       <c r="B15">
-        <v>96.3634234335866</v>
+        <v>94.5615666515892</v>
       </c>
       <c r="C15">
-        <v>100.19546481847</v>
+        <v>100.706926575867</v>
       </c>
       <c r="D15">
         <v>1.80565973772502</v>
@@ -583,10 +583,10 @@
         <v>1992-09</v>
       </c>
       <c r="B16">
-        <v>97.5936750687135</v>
+        <v>95.663353164387</v>
       </c>
       <c r="C16">
-        <v>100.404731297931</v>
+        <v>100.805921597261</v>
       </c>
       <c r="D16">
         <v>1.78443026015471</v>
@@ -597,10 +597,10 @@
         <v>1992-10</v>
       </c>
       <c r="B17">
-        <v>96.5213505244133</v>
+        <v>95.2126783206416</v>
       </c>
       <c r="C17">
-        <v>96.4508275557114</v>
+        <v>98.5569429870889</v>
       </c>
       <c r="D17">
         <v>1.66550493082332</v>
@@ -611,10 +611,10 @@
         <v>1992-11</v>
       </c>
       <c r="B18">
-        <v>96.3121450287167</v>
+        <v>95.3976015556494</v>
       </c>
       <c r="C18">
-        <v>93.9282573845825</v>
+        <v>98.6156219227106</v>
       </c>
       <c r="D18">
         <v>1.55048668928414</v>
@@ -625,10 +625,10 @@
         <v>1992-12</v>
       </c>
       <c r="B19">
-        <v>97.8481514189956</v>
+        <v>97.2495747993029</v>
       </c>
       <c r="C19">
-        <v>93.2137105953763</v>
+        <v>97.6843893380019</v>
       </c>
       <c r="D19">
         <v>1.43935062417874</v>
@@ -639,10 +639,10 @@
         <v>1993-01</v>
       </c>
       <c r="B20">
-        <v>97.9307253453364</v>
+        <v>97.3852987282941</v>
       </c>
       <c r="C20">
-        <v>96.2489097738828</v>
+        <v>100.556694971175</v>
       </c>
       <c r="D20">
         <v>1.3320722134699</v>
@@ -653,10 +653,10 @@
         <v>1993-02</v>
       </c>
       <c r="B21">
-        <v>98.4693832413643</v>
+        <v>97.9212090318884</v>
       </c>
       <c r="C21">
-        <v>99.2082716886092</v>
+        <v>104.648135734685</v>
       </c>
       <c r="D21">
         <v>1.25734333088667</v>
@@ -667,10 +667,10 @@
         <v>1993-03</v>
       </c>
       <c r="B22">
-        <v>94.4115513900566</v>
+        <v>94.2837703552301</v>
       </c>
       <c r="C22">
-        <v>101.540050124452</v>
+        <v>104.283525277213</v>
       </c>
       <c r="D22">
         <v>1.21493748398542</v>
@@ -681,10 +681,10 @@
         <v>1993-04</v>
       </c>
       <c r="B23">
-        <v>97.7525409315986</v>
+        <v>93.9599043882992</v>
       </c>
       <c r="C23">
-        <v>101.194825023881</v>
+        <v>103.793389559284</v>
       </c>
       <c r="D23">
         <v>1.2047008702184</v>
@@ -695,10 +695,10 @@
         <v>1993-05</v>
       </c>
       <c r="B24">
-        <v>98.2917531733738</v>
+        <v>98.202706976407</v>
       </c>
       <c r="C24">
-        <v>102.044341637931</v>
+        <v>104.772807781012</v>
       </c>
       <c r="D24">
         <v>1.18893568526393</v>
@@ -709,10 +709,10 @@
         <v>1993-06</v>
       </c>
       <c r="B25">
-        <v>97.9496938411545</v>
+        <v>98.5759433870695</v>
       </c>
       <c r="C25">
-        <v>104.44231963162</v>
+        <v>106.776691422629</v>
       </c>
       <c r="D25">
         <v>1.16767728470772</v>
@@ -723,10 +723,10 @@
         <v>1993-07</v>
       </c>
       <c r="B26">
-        <v>97.7026008275137</v>
+        <v>98.4949344224838</v>
       </c>
       <c r="C26">
-        <v>100.189022567103</v>
+        <v>104.121653821769</v>
       </c>
       <c r="D26">
         <v>1.14097280326038</v>
@@ -737,10 +737,10 @@
         <v>1993-08</v>
       </c>
       <c r="B27">
-        <v>97.3015317356837</v>
+        <v>96.3207053301941</v>
       </c>
       <c r="C27">
-        <v>101.503356951376</v>
+        <v>106.045953267322</v>
       </c>
       <c r="D27">
         <v>1.13849549154912</v>
@@ -751,10 +751,10 @@
         <v>1993-09</v>
       </c>
       <c r="B28">
-        <v>94.9924217349614</v>
+        <v>93.359638779978</v>
       </c>
       <c r="C28">
-        <v>102.211721427243</v>
+        <v>105.380013314722</v>
       </c>
       <c r="D28">
         <v>1.16013738328466</v>
@@ -765,10 +765,10 @@
         <v>1993-10</v>
       </c>
       <c r="B29">
-        <v>98.3511276293965</v>
+        <v>97.2409155288525</v>
       </c>
       <c r="C29">
-        <v>104.632013165818</v>
+        <v>107.981477373829</v>
       </c>
       <c r="D29">
         <v>1.20584401247335</v>
@@ -779,10 +779,10 @@
         <v>1993-11</v>
       </c>
       <c r="B30">
-        <v>99.6557561343061</v>
+        <v>98.5904930622547</v>
       </c>
       <c r="C30">
-        <v>106.154875639197</v>
+        <v>109.725633802735</v>
       </c>
       <c r="D30">
         <v>1.47600446870453</v>
@@ -793,10 +793,10 @@
         <v>1993-12</v>
       </c>
       <c r="B31">
-        <v>102.999696378646</v>
+        <v>102.672958146792</v>
       </c>
       <c r="C31">
-        <v>107.95707249397</v>
+        <v>109.804852131264</v>
       </c>
       <c r="D31">
         <v>1.97010043983225</v>
@@ -807,10 +807,10 @@
         <v>1994-01</v>
       </c>
       <c r="B32">
-        <v>105.509974002546</v>
+        <v>105.408879116196</v>
       </c>
       <c r="C32">
-        <v>105.642592217865</v>
+        <v>109.301930331054</v>
       </c>
       <c r="D32">
         <v>2.68758125810844</v>
@@ -821,10 +821,10 @@
         <v>1994-02</v>
       </c>
       <c r="B33">
-        <v>104.46968064225</v>
+        <v>104.8264455614</v>
       </c>
       <c r="C33">
-        <v>104.664980991077</v>
+        <v>106.831906507414</v>
       </c>
       <c r="D33">
         <v>3.16769776371919</v>
@@ -835,10 +835,10 @@
         <v>1994-03</v>
       </c>
       <c r="B34">
-        <v>106.697319700504</v>
+        <v>106.570942217639</v>
       </c>
       <c r="C34">
-        <v>106.503072334442</v>
+        <v>109.524824406935</v>
       </c>
       <c r="D34">
         <v>3.41104886989265</v>
@@ -849,10 +849,10 @@
         <v>1994-04</v>
       </c>
       <c r="B35">
-        <v>106.630903207785</v>
+        <v>108.112232137263</v>
       </c>
       <c r="C35">
-        <v>106.185021948005</v>
+        <v>108.031085872107</v>
       </c>
       <c r="D35">
         <v>3.41815828397355</v>
@@ -863,10 +863,10 @@
         <v>1994-05</v>
       </c>
       <c r="B36">
-        <v>103.789278082582</v>
+        <v>103.408543772821</v>
       </c>
       <c r="C36">
-        <v>105.799950731227</v>
+        <v>108.152011807169</v>
       </c>
       <c r="D36">
         <v>3.46419868796613</v>
@@ -877,10 +877,10 @@
         <v>1994-06</v>
       </c>
       <c r="B37">
-        <v>105.676941547423</v>
+        <v>105.745257419718</v>
       </c>
       <c r="C37">
-        <v>108.513888539376</v>
+        <v>109.354218540343</v>
       </c>
       <c r="D37">
         <v>3.54901764396236</v>
@@ -891,10 +891,10 @@
         <v>1994-07</v>
       </c>
       <c r="B38">
-        <v>104.134616116448</v>
+        <v>103.689201024497</v>
       </c>
       <c r="C38">
-        <v>106.160950951519</v>
+        <v>109.283590245456</v>
       </c>
       <c r="D38">
         <v>3.67239162123447</v>
@@ -905,10 +905,10 @@
         <v>1994-08</v>
       </c>
       <c r="B39">
-        <v>105.648133922083</v>
+        <v>105.964131433922</v>
       </c>
       <c r="C39">
-        <v>107.073942398183</v>
+        <v>108.375573312595</v>
       </c>
       <c r="D39">
         <v>3.79645026890971</v>
@@ -919,10 +919,10 @@
         <v>1994-09</v>
       </c>
       <c r="B40">
-        <v>107.822472827638</v>
+        <v>108.26952224398</v>
       </c>
       <c r="C40">
-        <v>108.428602692824</v>
+        <v>110.697238503446</v>
       </c>
       <c r="D40">
         <v>3.92123820565158</v>
@@ -933,10 +933,10 @@
         <v>1994-10</v>
       </c>
       <c r="B41">
-        <v>108.950234753362</v>
+        <v>110.622592921768</v>
       </c>
       <c r="C41">
-        <v>107.517452922962</v>
+        <v>109.302221925532</v>
       </c>
       <c r="D41">
         <v>4.04680036609322</v>
@@ -947,10 +947,10 @@
         <v>1994-11</v>
       </c>
       <c r="B42">
-        <v>108.661096144368</v>
+        <v>109.889673773627</v>
       </c>
       <c r="C42">
-        <v>110.685625473639</v>
+        <v>112.221021346121</v>
       </c>
       <c r="D42">
         <v>3.90328484047056</v>
@@ -961,10 +961,10 @@
         <v>1994-12</v>
       </c>
       <c r="B43">
-        <v>108.653663184214</v>
+        <v>110.127981521238</v>
       </c>
       <c r="C43">
-        <v>108.601501786177</v>
+        <v>110.679152771388</v>
       </c>
       <c r="D43">
         <v>3.49437908316152</v>
@@ -975,10 +975,10 @@
         <v>1995-01</v>
       </c>
       <c r="B44">
-        <v>107.181319705732</v>
+        <v>108.387458830224</v>
       </c>
       <c r="C44">
-        <v>108.339137543066</v>
+        <v>109.920039972795</v>
       </c>
       <c r="D44">
         <v>2.8272205449972</v>
@@ -989,10 +989,10 @@
         <v>1995-02</v>
       </c>
       <c r="B45">
-        <v>106.286714042407</v>
+        <v>107.356580973453</v>
       </c>
       <c r="C45">
-        <v>107.63543384898</v>
+        <v>108.384102526126</v>
       </c>
       <c r="D45">
         <v>2.43790329254678</v>
@@ -1003,10 +1003,10 @@
         <v>1995-03</v>
       </c>
       <c r="B46">
-        <v>108.245915724008</v>
+        <v>106.978313649984</v>
       </c>
       <c r="C46">
-        <v>103.916379405997</v>
+        <v>104.517389966436</v>
       </c>
       <c r="D46">
         <v>2.3192239192804</v>
@@ -1017,10 +1017,10 @@
         <v>1995-04</v>
       </c>
       <c r="B47">
-        <v>106.658233197441</v>
+        <v>108.603497181401</v>
       </c>
       <c r="C47">
-        <v>102.246554252735</v>
+        <v>104.531377842736</v>
       </c>
       <c r="D47">
         <v>2.46788840146823</v>
@@ -1031,10 +1031,10 @@
         <v>1995-05</v>
       </c>
       <c r="B48">
-        <v>106.52650092164</v>
+        <v>106.209524515943</v>
       </c>
       <c r="C48">
-        <v>100.855760828116</v>
+        <v>102.653005150334</v>
       </c>
       <c r="D48">
         <v>2.5720149018148</v>
@@ -1045,10 +1045,10 @@
         <v>1995-06</v>
       </c>
       <c r="B49">
-        <v>104.745854964546</v>
+        <v>103.999758505414</v>
       </c>
       <c r="C49">
-        <v>96.5501793253501</v>
+        <v>99.3542781215284</v>
       </c>
       <c r="D49">
         <v>2.63157447678421</v>
@@ -1059,10 +1059,10 @@
         <v>1995-07</v>
       </c>
       <c r="B50">
-        <v>103.311709201674</v>
+        <v>102.709867182862</v>
       </c>
       <c r="C50">
-        <v>96.0396606632802</v>
+        <v>97.7869497960633</v>
       </c>
       <c r="D50">
         <v>2.64672081193827</v>
@@ -1073,10 +1073,10 @@
         <v>1995-08</v>
       </c>
       <c r="B51">
-        <v>98.0443449466256</v>
+        <v>96.7050207456355</v>
       </c>
       <c r="C51">
-        <v>93.7527336779963</v>
+        <v>96.4996802111216</v>
       </c>
       <c r="D51">
         <v>2.61938592462714</v>
@@ -1087,10 +1087,10 @@
         <v>1995-09</v>
       </c>
       <c r="B52">
-        <v>97.1212540098931</v>
+        <v>95.144455164168</v>
       </c>
       <c r="C52">
-        <v>93.6226780905521</v>
+        <v>96.2223551638351</v>
       </c>
       <c r="D52">
         <v>2.54989309082461</v>
@@ -1101,10 +1101,10 @@
         <v>1995-10</v>
       </c>
       <c r="B53">
-        <v>100.129438444503</v>
+        <v>99.8308057347728</v>
       </c>
       <c r="C53">
-        <v>92.7725986011647</v>
+        <v>95.9172984941127</v>
       </c>
       <c r="D53">
         <v>2.43853268596574</v>
@@ -1115,10 +1115,10 @@
         <v>1995-11</v>
       </c>
       <c r="B54">
-        <v>92.9824368267545</v>
+        <v>90.2440250114051</v>
       </c>
       <c r="C54">
-        <v>89.3022726639487</v>
+        <v>92.0243117607178</v>
       </c>
       <c r="D54">
         <v>2.39166243627402</v>
@@ -1129,10 +1129,10 @@
         <v>1995-12</v>
       </c>
       <c r="B55">
-        <v>91.1767148997206</v>
+        <v>88.3893487450788</v>
       </c>
       <c r="C55">
-        <v>90.766418742602</v>
+        <v>93.3026019907237</v>
       </c>
       <c r="D55">
         <v>2.40884327854958</v>
@@ -1143,10 +1143,10 @@
         <v>1996-01</v>
       </c>
       <c r="B56">
-        <v>92.5234380040225</v>
+        <v>90.3948432351359</v>
       </c>
       <c r="C56">
-        <v>90.9041250514098</v>
+        <v>93.6082682199691</v>
       </c>
       <c r="D56">
         <v>2.48977093979059</v>
@@ -1157,10 +1157,10 @@
         <v>1996-02</v>
       </c>
       <c r="B57">
-        <v>88.1964515912565</v>
+        <v>85.1654451586265</v>
       </c>
       <c r="C57">
-        <v>90.9957093542956</v>
+        <v>93.6567873750737</v>
       </c>
       <c r="D57">
         <v>2.62310690416197</v>
@@ -1171,10 +1171,10 @@
         <v>1996-03</v>
       </c>
       <c r="B58">
-        <v>90.9635590876025</v>
+        <v>90.4512504418475</v>
       </c>
       <c r="C58">
-        <v>92.6286149440709</v>
+        <v>95.7848505910193</v>
       </c>
       <c r="D58">
         <v>2.8084886758643</v>
@@ -1185,10 +1185,10 @@
         <v>1996-04</v>
       </c>
       <c r="B59">
-        <v>91.4416919032278</v>
+        <v>89.5163986336019</v>
       </c>
       <c r="C59">
-        <v>92.0332978201312</v>
+        <v>94.6948388414987</v>
       </c>
       <c r="D59">
         <v>3.04547036236073</v>
@@ -1199,10 +1199,10 @@
         <v>1996-05</v>
       </c>
       <c r="B60">
-        <v>90.8520316462968</v>
+        <v>88.7581861150837</v>
       </c>
       <c r="C60">
-        <v>92.0212345243839</v>
+        <v>94.6460806416099</v>
       </c>
       <c r="D60">
         <v>3.16469887105231</v>
@@ -1213,10 +1213,10 @@
         <v>1996-06</v>
       </c>
       <c r="B61">
-        <v>89.936402811654</v>
+        <v>86.6624738907711</v>
       </c>
       <c r="C61">
-        <v>94.8889685632157</v>
+        <v>97.8290017604487</v>
       </c>
       <c r="D61">
         <v>3.16692908210572</v>
@@ -1227,10 +1227,10 @@
         <v>1996-07</v>
       </c>
       <c r="B62">
-        <v>91.377880603776</v>
+        <v>89.5922636142147</v>
       </c>
       <c r="C62">
-        <v>98.3333423629707</v>
+        <v>100.868036862739</v>
       </c>
       <c r="D62">
         <v>3.05308535901816</v>
@@ -1241,10 +1241,10 @@
         <v>1996-08</v>
       </c>
       <c r="B63">
-        <v>94.5381937125299</v>
+        <v>92.6533300745788</v>
       </c>
       <c r="C63">
-        <v>99.7591676722634</v>
+        <v>102.392513930175</v>
       </c>
       <c r="D63">
         <v>3.05694291607774</v>
@@ -1255,10 +1255,10 @@
         <v>1996-09</v>
       </c>
       <c r="B64">
-        <v>93.5333095789284</v>
+        <v>91.1132109335001</v>
       </c>
       <c r="C64">
-        <v>98.9926499451123</v>
+        <v>101.675663222428</v>
       </c>
       <c r="D64">
         <v>3.17767855337425</v>
@@ -1269,10 +1269,10 @@
         <v>1996-10</v>
       </c>
       <c r="B65">
-        <v>91.3330922454173</v>
+        <v>88.1161417495161</v>
       </c>
       <c r="C65">
-        <v>99.0197062152135</v>
+        <v>102.10490421778</v>
       </c>
       <c r="D65">
         <v>3.41484702067577</v>
@@ -1283,10 +1283,10 @@
         <v>1996-11</v>
       </c>
       <c r="B66">
-        <v>92.784093832014</v>
+        <v>89.4206186022969</v>
       </c>
       <c r="C66">
-        <v>100.752027431418</v>
+        <v>102.914489415218</v>
       </c>
       <c r="D66">
         <v>3.55275430318116</v>
@@ -1297,10 +1297,10 @@
         <v>1996-12</v>
       </c>
       <c r="B67">
-        <v>92.9794583238494</v>
+        <v>89.1580886859384</v>
       </c>
       <c r="C67">
-        <v>99.4455873768312</v>
+        <v>101.87320040715</v>
       </c>
       <c r="D67">
         <v>3.59174984817673</v>
@@ -1311,10 +1311,10 @@
         <v>1997-01</v>
       </c>
       <c r="B68">
-        <v>92.00514647117</v>
+        <v>87.5020777502643</v>
       </c>
       <c r="C68">
-        <v>99.1503678760453</v>
+        <v>100.668658804921</v>
       </c>
       <c r="D68">
         <v>3.53234716951336</v>
@@ -1325,10 +1325,10 @@
         <v>1997-02</v>
       </c>
       <c r="B69">
-        <v>93.6897769423789</v>
+        <v>90.691797199737</v>
       </c>
       <c r="C69">
-        <v>99.7386679515798</v>
+        <v>102.279624808208</v>
       </c>
       <c r="D69">
         <v>3.49145920871668</v>
@@ -1339,10 +1339,10 @@
         <v>1997-03</v>
       </c>
       <c r="B70">
-        <v>92.130832565353</v>
+        <v>88.9567032644823</v>
       </c>
       <c r="C70">
-        <v>100.085342616011</v>
+        <v>101.594946636087</v>
       </c>
       <c r="D70">
         <v>3.46902165460806</v>
@@ -1353,10 +1353,10 @@
         <v>1997-04</v>
       </c>
       <c r="B71">
-        <v>90.1779131212995</v>
+        <v>87.1213037792027</v>
       </c>
       <c r="C71">
-        <v>100.774307547409</v>
+        <v>102.39048205519</v>
       </c>
       <c r="D71">
         <v>3.46488441379078</v>
@@ -1367,10 +1367,10 @@
         <v>1997-05</v>
       </c>
       <c r="B72">
-        <v>93.9880600440012</v>
+        <v>91.5062172020637</v>
       </c>
       <c r="C72">
-        <v>101.31533786221</v>
+        <v>101.887299977432</v>
       </c>
       <c r="D72">
         <v>3.47941551538125</v>
@@ -1381,10 +1381,10 @@
         <v>1997-06</v>
       </c>
       <c r="B73">
-        <v>93.2767293463257</v>
+        <v>91.5233024846221</v>
       </c>
       <c r="C73">
-        <v>99.2352295824368</v>
+        <v>100.374164303369</v>
       </c>
       <c r="D73">
         <v>3.51245469834491</v>
@@ -1395,10 +1395,10 @@
         <v>1997-07</v>
       </c>
       <c r="B74">
-        <v>93.5529959699694</v>
+        <v>90.7600729359552</v>
       </c>
       <c r="C74">
-        <v>97.9495668933084</v>
+        <v>99.0142790111559</v>
       </c>
       <c r="D74">
         <v>3.56394071325157</v>
@@ -1409,10 +1409,10 @@
         <v>1997-08</v>
       </c>
       <c r="B75">
-        <v>94.340016086504</v>
+        <v>91.6022341318175</v>
       </c>
       <c r="C75">
-        <v>99.237513503464</v>
+        <v>100.806941227297</v>
       </c>
       <c r="D75">
         <v>3.58344043865308</v>
@@ -1423,10 +1423,10 @@
         <v>1997-09</v>
       </c>
       <c r="B76">
-        <v>95.6293984418355</v>
+        <v>93.3843445843906</v>
       </c>
       <c r="C76">
-        <v>101.071359134395</v>
+        <v>102.536224286976</v>
       </c>
       <c r="D76">
         <v>3.57114724540007</v>
@@ -1437,10 +1437,10 @@
         <v>1997-10</v>
       </c>
       <c r="B77">
-        <v>99.5326300493137</v>
+        <v>98.3037370454272</v>
       </c>
       <c r="C77">
-        <v>103.294833927267</v>
+        <v>104.137987907811</v>
       </c>
       <c r="D77">
         <v>3.52736718296744</v>
@@ -1451,10 +1451,10 @@
         <v>1997-11</v>
       </c>
       <c r="B78">
-        <v>97.0801446806152</v>
+        <v>95.0726205658599</v>
       </c>
       <c r="C78">
-        <v>101.735811260726</v>
+        <v>103.504347657113</v>
       </c>
       <c r="D78">
         <v>3.43807146483699</v>
@@ -1465,10 +1465,10 @@
         <v>1997-12</v>
       </c>
       <c r="B79">
-        <v>94.9400176978749</v>
+        <v>92.1180326545129</v>
       </c>
       <c r="C79">
-        <v>101.367004430289</v>
+        <v>102.239045696156</v>
       </c>
       <c r="D79">
         <v>3.30347541986364</v>
@@ -1479,10 +1479,10 @@
         <v>1998-01</v>
       </c>
       <c r="B80">
-        <v>88.7878815291328</v>
+        <v>84.3170473315534</v>
       </c>
       <c r="C80">
-        <v>96.6881222525749</v>
+        <v>99.0548858095589</v>
       </c>
       <c r="D80">
         <v>3.12361053453839</v>
@@ -1493,10 +1493,10 @@
         <v>1998-02</v>
       </c>
       <c r="B81">
-        <v>86.9374632249023</v>
+        <v>81.6336155518194</v>
       </c>
       <c r="C81">
-        <v>95.3498358763951</v>
+        <v>97.1156383523861</v>
       </c>
       <c r="D81">
         <v>2.89814080828373</v>
@@ -1507,10 +1507,10 @@
         <v>1998-03</v>
       </c>
       <c r="B82">
-        <v>85.4494488450984</v>
+        <v>79.724651597019</v>
       </c>
       <c r="C82">
-        <v>93.3374676760387</v>
+        <v>95.3861337219717</v>
       </c>
       <c r="D82">
         <v>2.62805912952824</v>
@@ -1521,10 +1521,10 @@
         <v>1998-04</v>
       </c>
       <c r="B83">
-        <v>84.795297965863</v>
+        <v>78.7093267338622</v>
       </c>
       <c r="C83">
-        <v>92.6994157501779</v>
+        <v>94.440219080028</v>
       </c>
       <c r="D83">
         <v>2.31460292663537</v>
@@ -1535,10 +1535,10 @@
         <v>1998-05</v>
       </c>
       <c r="B84">
-        <v>97.6954125544</v>
+        <v>97.7824297192458</v>
       </c>
       <c r="C84">
-        <v>93.867236107054</v>
+        <v>94.047844507623</v>
       </c>
       <c r="D84">
         <v>2.11515932023812</v>
@@ -1549,10 +1549,10 @@
         <v>1998-06</v>
       </c>
       <c r="B85">
-        <v>99.0573521888044</v>
+        <v>98.9131200415645</v>
       </c>
       <c r="C85">
-        <v>95.1147951413315</v>
+        <v>94.8747966621073</v>
       </c>
       <c r="D85">
         <v>2.02805315549546</v>
@@ -1563,10 +1563,10 @@
         <v>1998-07</v>
       </c>
       <c r="B86">
-        <v>95.0485593387748</v>
+        <v>94.665093464202</v>
       </c>
       <c r="C86">
-        <v>94.3821376953364</v>
+        <v>94.8399049463975</v>
       </c>
       <c r="D86">
         <v>2.05209916057791</v>
@@ -1577,10 +1577,10 @@
         <v>1998-08</v>
       </c>
       <c r="B87">
-        <v>95.2756681987235</v>
+        <v>94.3913043954862</v>
       </c>
       <c r="C87">
-        <v>92.8444299258443</v>
+        <v>93.6546475033648</v>
       </c>
       <c r="D87">
         <v>2.0933544721517</v>
@@ -1591,10 +1591,10 @@
         <v>1998-09</v>
       </c>
       <c r="B88">
-        <v>96.8824067095509</v>
+        <v>97.9756142334824</v>
       </c>
       <c r="C88">
-        <v>89.8742404754912</v>
+        <v>92.1475055018584</v>
       </c>
       <c r="D88">
         <v>2.15164951003557</v>
@@ -1605,10 +1605,10 @@
         <v>1998-10</v>
       </c>
       <c r="B89">
-        <v>94.439051170518</v>
+        <v>94.9763007913092</v>
       </c>
       <c r="C89">
-        <v>87.6506189194674</v>
+        <v>89.3059970436272</v>
       </c>
       <c r="D89">
         <v>2.22678618106913</v>
@@ -1619,10 +1619,10 @@
         <v>1998-11</v>
       </c>
       <c r="B90">
-        <v>96.392127257197</v>
+        <v>98.2074536009264</v>
       </c>
       <c r="C90">
-        <v>86.182209449208</v>
+        <v>89.7540952346293</v>
       </c>
       <c r="D90">
         <v>2.32713229329462</v>
@@ -1633,10 +1633,10 @@
         <v>1998-12</v>
       </c>
       <c r="B91">
-        <v>96.765663420745</v>
+        <v>98.123024655265</v>
       </c>
       <c r="C91">
-        <v>87.676054485841</v>
+        <v>91.0711567500001</v>
       </c>
       <c r="D91">
         <v>2.45286912564227</v>
@@ -1647,10 +1647,10 @@
         <v>1999-01</v>
       </c>
       <c r="B92">
-        <v>104.160047472753</v>
+        <v>107.176390428043</v>
       </c>
       <c r="C92">
-        <v>91.6610375104313</v>
+        <v>95.1495036755686</v>
       </c>
       <c r="D92">
         <v>2.60434649908079</v>
@@ -1661,10 +1661,10 @@
         <v>1999-02</v>
       </c>
       <c r="B93">
-        <v>104.263316491459</v>
+        <v>105.211659926829</v>
       </c>
       <c r="C93">
-        <v>93.8260244141855</v>
+        <v>96.7805946418639</v>
       </c>
       <c r="D93">
         <v>2.74351642396778</v>
@@ -1675,10 +1675,10 @@
         <v>1999-03</v>
       </c>
       <c r="B94">
-        <v>105.702132264225</v>
+        <v>106.803372387621</v>
       </c>
       <c r="C94">
-        <v>95.8897015505166</v>
+        <v>98.1444437107376</v>
       </c>
       <c r="D94">
         <v>2.87017518849085</v>
@@ -1689,10 +1689,10 @@
         <v>1999-04</v>
       </c>
       <c r="B95">
-        <v>97.7467718819626</v>
+        <v>97.933412261684</v>
       </c>
       <c r="C95">
-        <v>95.548294273923</v>
+        <v>99.7623883906373</v>
       </c>
       <c r="D95">
         <v>2.98415828271617</v>
@@ -1703,10 +1703,10 @@
         <v>1999-05</v>
       </c>
       <c r="B96">
-        <v>109.329837335125</v>
+        <v>110.833712152091</v>
       </c>
       <c r="C96">
-        <v>100.587886827969</v>
+        <v>105.287192738056</v>
       </c>
       <c r="D96">
         <v>3.12584775705349</v>
@@ -1717,10 +1717,10 @@
         <v>1999-06</v>
       </c>
       <c r="B97">
-        <v>120.158170583463</v>
+        <v>122.133903210953</v>
       </c>
       <c r="C97">
-        <v>104.893489499478</v>
+        <v>108.127622369844</v>
       </c>
       <c r="D97">
         <v>3.29493210203653</v>
@@ -1731,10 +1731,10 @@
         <v>1999-07</v>
       </c>
       <c r="B98">
-        <v>125.157730640014</v>
+        <v>127.546791764418</v>
       </c>
       <c r="C98">
-        <v>109.012416246449</v>
+        <v>114.022463831697</v>
       </c>
       <c r="D98">
         <v>3.49103793262128</v>
@@ -1745,10 +1745,10 @@
         <v>1999-08</v>
       </c>
       <c r="B99">
-        <v>125.606985730097</v>
+        <v>127.988448235866</v>
       </c>
       <c r="C99">
-        <v>105.326115593502</v>
+        <v>108.715372347093</v>
       </c>
       <c r="D99">
         <v>3.62536753886786</v>
@@ -1759,10 +1759,10 @@
         <v>1999-09</v>
       </c>
       <c r="B100">
-        <v>125.55850866043</v>
+        <v>127.500540864916</v>
       </c>
       <c r="C100">
-        <v>104.544823062664</v>
+        <v>107.328274120966</v>
       </c>
       <c r="D100">
         <v>3.69828346296369</v>
@@ -1773,10 +1773,10 @@
         <v>1999-10</v>
       </c>
       <c r="B101">
-        <v>130.817756501448</v>
+        <v>133.222620505194</v>
       </c>
       <c r="C101">
-        <v>105.816846793902</v>
+        <v>107.361244688858</v>
       </c>
       <c r="D101">
         <v>3.71031490160388</v>
@@ -1787,10 +1787,10 @@
         <v>1999-11</v>
       </c>
       <c r="B102">
-        <v>127.991245897305</v>
+        <v>129.540742946765</v>
       </c>
       <c r="C102">
-        <v>107.877855310328</v>
+        <v>110.388536292988</v>
       </c>
       <c r="D102">
         <v>3.80099198042805</v>
@@ -1801,10 +1801,10 @@
         <v>1999-12</v>
       </c>
       <c r="B103">
-        <v>125.739905043392</v>
+        <v>127.430975336663</v>
       </c>
       <c r="C103">
-        <v>108.339764260301</v>
+        <v>109.515737747838</v>
       </c>
       <c r="D103">
         <v>3.9698392503396</v>
@@ -1815,10 +1815,10 @@
         <v>2000-01</v>
       </c>
       <c r="B104">
-        <v>127.986937485144</v>
+        <v>129.476287219157</v>
       </c>
       <c r="C104">
-        <v>110.088816613322</v>
+        <v>110.284652247373</v>
       </c>
       <c r="D104">
         <v>4.21678949135216</v>
@@ -1829,10 +1829,10 @@
         <v>2000-02</v>
       </c>
       <c r="B105">
-        <v>128.558902375096</v>
+        <v>130.744609419377</v>
       </c>
       <c r="C105">
-        <v>114.724103378341</v>
+        <v>114.693618185696</v>
       </c>
       <c r="D105">
         <v>4.4485963992676</v>
@@ -1843,10 +1843,10 @@
         <v>2000-03</v>
       </c>
       <c r="B106">
-        <v>122.670270370899</v>
+        <v>123.869200582271</v>
       </c>
       <c r="C106">
-        <v>110.142859325391</v>
+        <v>109.389302691505</v>
       </c>
       <c r="D106">
         <v>4.66506074546319</v>
@@ -1857,10 +1857,10 @@
         <v>2000-04</v>
       </c>
       <c r="B107">
-        <v>130.880162699453</v>
+        <v>133.50898831267</v>
       </c>
       <c r="C107">
-        <v>116.504273109559</v>
+        <v>115.937534005146</v>
       </c>
       <c r="D107">
         <v>4.86602114815209</v>
@@ -1871,10 +1871,10 @@
         <v>2000-05</v>
       </c>
       <c r="B108">
-        <v>128.972315607026</v>
+        <v>130.872748486562</v>
       </c>
       <c r="C108">
-        <v>115.453126899831</v>
+        <v>115.552828284284</v>
       </c>
       <c r="D108">
         <v>4.893614697928</v>
@@ -1885,10 +1885,10 @@
         <v>2000-06</v>
       </c>
       <c r="B109">
-        <v>119.356395392771</v>
+        <v>120.286166762135</v>
       </c>
       <c r="C109">
-        <v>104.758301040451</v>
+        <v>106.805721582031</v>
       </c>
       <c r="D109">
         <v>4.74940209995216</v>
@@ -1899,10 +1899,10 @@
         <v>2000-07</v>
       </c>
       <c r="B110">
-        <v>119.289847823247</v>
+        <v>120.598549960017</v>
       </c>
       <c r="C110">
-        <v>100.511087484753</v>
+        <v>101.026565610208</v>
       </c>
       <c r="D110">
         <v>4.43560207735563</v>
@@ -1913,10 +1913,10 @@
         <v>2000-08</v>
       </c>
       <c r="B111">
-        <v>119.681077271936</v>
+        <v>121.822606073166</v>
       </c>
       <c r="C111">
-        <v>102.686888794662</v>
+        <v>102.737037581048</v>
       </c>
       <c r="D111">
         <v>4.17297017092861</v>
@@ -1927,10 +1927,10 @@
         <v>2000-09</v>
       </c>
       <c r="B112">
-        <v>112.461530131397</v>
+        <v>112.981120543709</v>
       </c>
       <c r="C112">
-        <v>98.8076027815279</v>
+        <v>99.8037112538115</v>
       </c>
       <c r="D112">
         <v>3.96076041292019</v>
@@ -1941,10 +1941,10 @@
         <v>2000-10</v>
       </c>
       <c r="B113">
-        <v>110.765990240919</v>
+        <v>111.817254800841</v>
       </c>
       <c r="C113">
-        <v>98.7513031131733</v>
+        <v>99.3076888810515</v>
       </c>
       <c r="D113">
         <v>3.79827474801753</v>
@@ -1955,10 +1955,10 @@
         <v>2000-11</v>
       </c>
       <c r="B114">
-        <v>109.468312285681</v>
+        <v>109.801549051042</v>
       </c>
       <c r="C114">
-        <v>97.5114034277409</v>
+        <v>97.7736819814907</v>
       </c>
       <c r="D114">
         <v>3.62176264094505</v>
@@ -1969,10 +1969,10 @@
         <v>2000-12</v>
       </c>
       <c r="B115">
-        <v>104.355582034921</v>
+        <v>104.142431526779</v>
       </c>
       <c r="C115">
-        <v>95.3209904464495</v>
+        <v>97.056300757994</v>
       </c>
       <c r="D115">
         <v>3.43133226446821</v>
@@ -1983,10 +1983,10 @@
         <v>2001-01</v>
       </c>
       <c r="B116">
-        <v>100.226938733018</v>
+        <v>100.000129645827</v>
       </c>
       <c r="C116">
-        <v>93.3029047024802</v>
+        <v>94.0383770518756</v>
       </c>
       <c r="D116">
         <v>3.22708154945654</v>
@@ -1997,10 +1997,10 @@
         <v>2001-02</v>
       </c>
       <c r="B117">
-        <v>92.3374193724904</v>
+        <v>92.0469473626765</v>
       </c>
       <c r="C117">
-        <v>88.4445152029</v>
+        <v>90.0158927164757</v>
       </c>
       <c r="D117">
         <v>2.97903242616884</v>
@@ -2011,10 +2011,10 @@
         <v>2001-03</v>
       </c>
       <c r="B118">
-        <v>88.9455464437475</v>
+        <v>88.5177606976264</v>
       </c>
       <c r="C118">
-        <v>87.5688927599925</v>
+        <v>88.7515136511399</v>
       </c>
       <c r="D118">
         <v>2.68788559435218</v>
@@ -2025,10 +2025,10 @@
         <v>2001-04</v>
       </c>
       <c r="B119">
-        <v>84.5048237112759</v>
+        <v>83.845370206524</v>
       </c>
       <c r="C119">
-        <v>80.1959749965288</v>
+        <v>81.4899975437476</v>
       </c>
       <c r="D119">
         <v>2.35439669275085</v>
@@ -2039,10 +2039,10 @@
         <v>2001-05</v>
       </c>
       <c r="B120">
-        <v>83.8915365701152</v>
+        <v>82.7360751137308</v>
       </c>
       <c r="C120">
-        <v>78.376022154492</v>
+        <v>81.3906171913999</v>
       </c>
       <c r="D120">
         <v>2.07715130054515</v>
@@ -2053,10 +2053,10 @@
         <v>2001-06</v>
       </c>
       <c r="B121">
-        <v>81.6921033828923</v>
+        <v>80.5082434491961</v>
       </c>
       <c r="C121">
-        <v>82.360872867112</v>
+        <v>84.4249362276688</v>
       </c>
       <c r="D121">
         <v>1.85476912483841</v>
@@ -2067,10 +2067,10 @@
         <v>2001-07</v>
       </c>
       <c r="B122">
-        <v>82.3274294635523</v>
+        <v>81.3552816943266</v>
       </c>
       <c r="C122">
-        <v>82.8923253609219</v>
+        <v>85.4637399697614</v>
       </c>
       <c r="D122">
         <v>1.6862064217767</v>
@@ -2081,10 +2081,10 @@
         <v>2001-08</v>
       </c>
       <c r="B123">
-        <v>79.8267243135346</v>
+        <v>78.4710377364152</v>
       </c>
       <c r="C123">
-        <v>83.4042861813973</v>
+        <v>84.2529517352396</v>
       </c>
       <c r="D123">
         <v>1.52997008734708</v>
@@ -2095,10 +2095,10 @@
         <v>2001-09</v>
       </c>
       <c r="B124">
-        <v>84.5132076676456</v>
+        <v>83.5348511632002</v>
       </c>
       <c r="C124">
-        <v>85.7589479235662</v>
+        <v>87.1003810140519</v>
       </c>
       <c r="D124">
         <v>1.3861572064219</v>
@@ -2109,10 +2109,10 @@
         <v>2001-10</v>
       </c>
       <c r="B125">
-        <v>78.3034181971777</v>
+        <v>76.6710619321975</v>
       </c>
       <c r="C125">
-        <v>80.9044430369406</v>
+        <v>83.1560561541259</v>
       </c>
       <c r="D125">
         <v>1.25483839067257</v>
@@ -2123,10 +2123,10 @@
         <v>2001-11</v>
       </c>
       <c r="B126">
-        <v>80.2139402079585</v>
+        <v>79.5963473298418</v>
       </c>
       <c r="C126">
-        <v>78.254639106267</v>
+        <v>79.6636622959647</v>
       </c>
       <c r="D126">
         <v>1.19520326178734</v>
@@ -2137,10 +2137,10 @@
         <v>2001-12</v>
       </c>
       <c r="B127">
-        <v>81.4569996321704</v>
+        <v>80.3327193814279</v>
       </c>
       <c r="C127">
-        <v>77.4158652362446</v>
+        <v>79.6864399971369</v>
       </c>
       <c r="D127">
         <v>1.2067371616729</v>
@@ -2151,10 +2151,10 @@
         <v>2002-01</v>
       </c>
       <c r="B128">
-        <v>86.5872996571608</v>
+        <v>85.9678504962188</v>
       </c>
       <c r="C128">
-        <v>87.1884599599985</v>
+        <v>90.7793317909149</v>
       </c>
       <c r="D128">
         <v>1.28903670454234</v>
@@ -2165,10 +2165,10 @@
         <v>2002-02</v>
       </c>
       <c r="B129">
-        <v>89.3275789819871</v>
+        <v>88.2817168936414</v>
       </c>
       <c r="C129">
-        <v>90.883650499929</v>
+        <v>92.8842370188621</v>
       </c>
       <c r="D129">
         <v>1.40336458253097</v>
@@ -2179,10 +2179,10 @@
         <v>2002-03</v>
       </c>
       <c r="B130">
-        <v>96.3486068591704</v>
+        <v>95.8121553846499</v>
       </c>
       <c r="C130">
-        <v>99.1851411104575</v>
+        <v>100.478968594554</v>
       </c>
       <c r="D130">
         <v>1.54963958709816</v>
@@ -2193,10 +2193,10 @@
         <v>2002-04</v>
       </c>
       <c r="B131">
-        <v>104.602224093139</v>
+        <v>104.519167917556</v>
       </c>
       <c r="C131">
-        <v>104.772558551216</v>
+        <v>106.797934602631</v>
       </c>
       <c r="D131">
         <v>1.72781571669832</v>
@@ -2207,10 +2207,10 @@
         <v>2002-05</v>
       </c>
       <c r="B132">
-        <v>106.876613289777</v>
+        <v>107.731193265668</v>
       </c>
       <c r="C132">
-        <v>111.080209839144</v>
+        <v>112.819391088661</v>
       </c>
       <c r="D132">
         <v>1.93176729906095</v>
@@ -2221,10 +2221,10 @@
         <v>2002-06</v>
       </c>
       <c r="B133">
-        <v>107.272562321235</v>
+        <v>108.208209007255</v>
       </c>
       <c r="C133">
-        <v>111.220457421657</v>
+        <v>112.329188491823</v>
       </c>
       <c r="D133">
         <v>2.16172046631146</v>
@@ -2235,10 +2235,10 @@
         <v>2002-07</v>
       </c>
       <c r="B134">
-        <v>106.41077094301</v>
+        <v>106.673996188293</v>
       </c>
       <c r="C134">
-        <v>109.33197032505</v>
+        <v>110.632651388973</v>
       </c>
       <c r="D134">
         <v>2.41797189439046</v>
@@ -2249,10 +2249,10 @@
         <v>2002-08</v>
       </c>
       <c r="B135">
-        <v>104.951688963954</v>
+        <v>105.33412355033</v>
       </c>
       <c r="C135">
-        <v>107.34544503808</v>
+        <v>108.807282257989</v>
       </c>
       <c r="D135">
         <v>2.59015738647877</v>
@@ -2263,10 +2263,10 @@
         <v>2002-09</v>
       </c>
       <c r="B136">
-        <v>102.361727738991</v>
+        <v>102.828198982316</v>
       </c>
       <c r="C136">
-        <v>102.825707460759</v>
+        <v>104.541538608468</v>
       </c>
       <c r="D136">
         <v>2.67809501353841</v>
@@ -2277,10 +2277,10 @@
         <v>2002-10</v>
       </c>
       <c r="B137">
-        <v>104.083400285555</v>
+        <v>104.319218053184</v>
       </c>
       <c r="C137">
-        <v>104.305092689752</v>
+        <v>106.164585405036</v>
       </c>
       <c r="D137">
         <v>2.68183696301909</v>
@@ -2291,10 +2291,10 @@
         <v>2002-11</v>
       </c>
       <c r="B138">
-        <v>101.825125326427</v>
+        <v>102.432614733164</v>
       </c>
       <c r="C138">
-        <v>106.021058829342</v>
+        <v>107.784677426717</v>
       </c>
       <c r="D138">
         <v>2.65970183400532</v>
@@ -2305,10 +2305,10 @@
         <v>2002-12</v>
       </c>
       <c r="B139">
-        <v>102.18618416377</v>
+        <v>103.430440575541</v>
       </c>
       <c r="C139">
-        <v>107.619042238709</v>
+        <v>109.82959674582</v>
       </c>
       <c r="D139">
         <v>2.61184348512489</v>
@@ -2319,10 +2319,10 @@
         <v>2003-01</v>
       </c>
       <c r="B140">
-        <v>99.966691268594</v>
+        <v>100.263071031226</v>
       </c>
       <c r="C140">
-        <v>102.723225644508</v>
+        <v>104.532283651952</v>
       </c>
       <c r="D140">
         <v>2.53848389173652</v>
@@ -2333,10 +2333,10 @@
         <v>2003-02</v>
       </c>
       <c r="B141">
-        <v>98.725679927495</v>
+        <v>99.3791081184094</v>
       </c>
       <c r="C141">
-        <v>101.966643077062</v>
+        <v>104.267657673526</v>
       </c>
       <c r="D141">
         <v>2.42903239688179</v>
@@ -2347,10 +2347,10 @@
         <v>2003-03</v>
       </c>
       <c r="B142">
-        <v>96.8280905180392</v>
+        <v>96.9931216586362</v>
       </c>
       <c r="C142">
-        <v>101.72140338535</v>
+        <v>103.108335923055</v>
       </c>
       <c r="D142">
         <v>2.28381681316532</v>
@@ -2361,10 +2361,10 @@
         <v>2003-04</v>
       </c>
       <c r="B143">
-        <v>93.6185208039806</v>
+        <v>93.7894757583132</v>
       </c>
       <c r="C143">
-        <v>97.1971094307026</v>
+        <v>98.2161126556074</v>
       </c>
       <c r="D143">
         <v>2.10319065552376</v>
@@ -2375,10 +2375,10 @@
         <v>2003-05</v>
       </c>
       <c r="B144">
-        <v>91.5597198844274</v>
+        <v>92.215650516648</v>
       </c>
       <c r="C144">
-        <v>91.7297625599367</v>
+        <v>92.8678660581078</v>
       </c>
       <c r="D144">
         <v>2.07681629111758</v>
@@ -2389,10 +2389,10 @@
         <v>2003-06</v>
       </c>
       <c r="B145">
-        <v>91.1880028499251</v>
+        <v>90.8029013167925</v>
       </c>
       <c r="C145">
-        <v>91.8730557197769</v>
+        <v>93.6779149762503</v>
       </c>
       <c r="D145">
         <v>2.20344431259505</v>
@@ -2403,10 +2403,10 @@
         <v>2003-07</v>
       </c>
       <c r="B146">
-        <v>94.0441234337392</v>
+        <v>94.191728944111</v>
       </c>
       <c r="C146">
-        <v>95.9270940416627</v>
+        <v>96.7725990133438</v>
       </c>
       <c r="D146">
         <v>2.48201886265034</v>
@@ -2417,10 +2417,10 @@
         <v>2003-08</v>
       </c>
       <c r="B147">
-        <v>97.3684629968612</v>
+        <v>97.508203164204</v>
       </c>
       <c r="C147">
-        <v>98.0260763430284</v>
+        <v>98.7505494623147</v>
       </c>
       <c r="D147">
         <v>2.76286323333954</v>
@@ -2431,10 +2431,10 @@
         <v>2003-09</v>
       </c>
       <c r="B148">
-        <v>101.856655177553</v>
+        <v>102.187818475887</v>
       </c>
       <c r="C148">
-        <v>104.402672616874</v>
+        <v>104.435292482042</v>
       </c>
       <c r="D148">
         <v>3.046264699335</v>
@@ -2445,10 +2445,10 @@
         <v>2003-10</v>
       </c>
       <c r="B149">
-        <v>104.294598751655</v>
+        <v>104.804671256451</v>
       </c>
       <c r="C149">
-        <v>106.193712910697</v>
+        <v>106.570208405329</v>
       </c>
       <c r="D149">
         <v>3.33251401723309</v>
@@ -2459,10 +2459,10 @@
         <v>2003-11</v>
       </c>
       <c r="B150">
-        <v>111.688166274511</v>
+        <v>112.131548672035</v>
       </c>
       <c r="C150">
-        <v>110.796113408843</v>
+        <v>111.721839117557</v>
       </c>
       <c r="D150">
         <v>3.560266818271</v>
@@ -2473,10 +2473,10 @@
         <v>2003-12</v>
       </c>
       <c r="B151">
-        <v>110.290840363687</v>
+        <v>110.750353891102</v>
       </c>
       <c r="C151">
-        <v>110.254096635325</v>
+        <v>110.248353482732</v>
       </c>
       <c r="D151">
         <v>3.72963022021668</v>
@@ -2487,10 +2487,10 @@
         <v>2004-01</v>
       </c>
       <c r="B152">
-        <v>114.710029619354</v>
+        <v>114.653153788405</v>
       </c>
       <c r="C152">
-        <v>111.677980134996</v>
+        <v>111.987250827811</v>
       </c>
       <c r="D152">
         <v>3.84078010774476</v>
@@ -2501,10 +2501,10 @@
         <v>2004-02</v>
       </c>
       <c r="B153">
-        <v>112.350327143543</v>
+        <v>112.550090216364</v>
       </c>
       <c r="C153">
-        <v>106.773241304224</v>
+        <v>107.28604992415</v>
       </c>
       <c r="D153">
         <v>3.97440045626939</v>
@@ -2515,10 +2515,10 @@
         <v>2004-03</v>
       </c>
       <c r="B154">
-        <v>113.750519492104</v>
+        <v>114.003952932659</v>
       </c>
       <c r="C154">
-        <v>107.507027756523</v>
+        <v>108.034520962019</v>
       </c>
       <c r="D154">
         <v>4.13047424257111</v>
@@ -2529,10 +2529,10 @@
         <v>2004-04</v>
       </c>
       <c r="B155">
-        <v>114.112036749768</v>
+        <v>114.320493586061</v>
       </c>
       <c r="C155">
-        <v>110.022300437768</v>
+        <v>110.65764712287</v>
       </c>
       <c r="D155">
         <v>4.30901397089609</v>
@@ -2543,10 +2543,10 @@
         <v>2004-05</v>
       </c>
       <c r="B156">
-        <v>119.517116800799</v>
+        <v>119.43239143923</v>
       </c>
       <c r="C156">
-        <v>114.68156461731</v>
+        <v>115.128014856638</v>
       </c>
       <c r="D156">
         <v>4.34986723643307</v>
@@ -2557,10 +2557,10 @@
         <v>2004-06</v>
       </c>
       <c r="B157">
-        <v>118.151781303016</v>
+        <v>117.444302995589</v>
       </c>
       <c r="C157">
-        <v>115.029758196628</v>
+        <v>115.402181243655</v>
       </c>
       <c r="D157">
         <v>4.25386876492536</v>
@@ -2571,10 +2571,10 @@
         <v>2004-07</v>
       </c>
       <c r="B158">
-        <v>117.976985757484</v>
+        <v>117.839545888331</v>
       </c>
       <c r="C158">
-        <v>113.610360163655</v>
+        <v>114.683490884534</v>
       </c>
       <c r="D158">
         <v>4.02290413269012</v>
@@ -2585,10 +2585,10 @@
         <v>2004-08</v>
       </c>
       <c r="B159">
-        <v>115.376593167693</v>
+        <v>115.326316250719</v>
       </c>
       <c r="C159">
-        <v>109.11680200826</v>
+        <v>109.59732709814</v>
       </c>
       <c r="D159">
         <v>3.81927341732523</v>
@@ -2599,10 +2599,10 @@
         <v>2004-09</v>
       </c>
       <c r="B160">
-        <v>114.813924065653</v>
+        <v>114.792954860812</v>
       </c>
       <c r="C160">
-        <v>108.024561232825</v>
+        <v>107.826395572857</v>
       </c>
       <c r="D160">
         <v>3.64240215830745</v>
@@ -2613,10 +2613,10 @@
         <v>2004-10</v>
       </c>
       <c r="B161">
-        <v>112.35180244067</v>
+        <v>112.572669257824</v>
       </c>
       <c r="C161">
-        <v>106.390587891212</v>
+        <v>106.04394281931</v>
       </c>
       <c r="D161">
         <v>3.49177744399445</v>
@@ -2627,10 +2627,10 @@
         <v>2004-11</v>
       </c>
       <c r="B162">
-        <v>107.261143055494</v>
+        <v>106.978938775184</v>
       </c>
       <c r="C162">
-        <v>101.188462202165</v>
+        <v>101.589797811557</v>
       </c>
       <c r="D162">
         <v>3.40261251049037</v>
@@ -2641,10 +2641,10 @@
         <v>2004-12</v>
       </c>
       <c r="B163">
-        <v>105.288790436073</v>
+        <v>103.994690574546</v>
       </c>
       <c r="C163">
-        <v>100.443497487528</v>
+        <v>100.635329778224</v>
       </c>
       <c r="D163">
         <v>3.37415330425806</v>
@@ -2655,10 +2655,10 @@
         <v>2005-01</v>
       </c>
       <c r="B164">
-        <v>103.700275908766</v>
+        <v>103.607485741798</v>
       </c>
       <c r="C164">
-        <v>99.3285546035304</v>
+        <v>99.2811372310448</v>
       </c>
       <c r="D164">
         <v>3.40578609091871</v>
@@ -2669,10 +2669,10 @@
         <v>2005-02</v>
       </c>
       <c r="B165">
-        <v>108.527306368609</v>
+        <v>108.51079691427</v>
       </c>
       <c r="C165">
-        <v>104.834473708145</v>
+        <v>105.970177528475</v>
       </c>
       <c r="D165">
         <v>3.43258218634234</v>
@@ -2683,10 +2683,10 @@
         <v>2005-03</v>
       </c>
       <c r="B166">
-        <v>108.552750527926</v>
+        <v>108.199258570968</v>
       </c>
       <c r="C166">
-        <v>105.740906565705</v>
+        <v>106.886073422949</v>
       </c>
       <c r="D166">
         <v>3.45458257801519</v>
@@ -2697,10 +2697,10 @@
         <v>2005-04</v>
       </c>
       <c r="B167">
-        <v>107.150185697882</v>
+        <v>107.49976004261</v>
       </c>
       <c r="C167">
-        <v>103.125601441379</v>
+        <v>104.243724368241</v>
       </c>
       <c r="D167">
         <v>3.4718278184926</v>
@@ -2711,10 +2711,10 @@
         <v>2005-05</v>
       </c>
       <c r="B168">
-        <v>101.796551763501</v>
+        <v>101.859702930214</v>
       </c>
       <c r="C168">
-        <v>97.2422425017463</v>
+        <v>98.3072671686808</v>
       </c>
       <c r="D168">
         <v>3.51116223968795</v>
@@ -2725,10 +2725,10 @@
         <v>2005-06</v>
       </c>
       <c r="B169">
-        <v>102.225870361758</v>
+        <v>102.222016597821</v>
       </c>
       <c r="C169">
-        <v>96.9550615015218</v>
+        <v>97.9279944265822</v>
       </c>
       <c r="D169">
         <v>3.57240167096191</v>
@@ -2739,10 +2739,10 @@
         <v>2005-07</v>
       </c>
       <c r="B170">
-        <v>102.598805968353</v>
+        <v>102.661015633747</v>
       </c>
       <c r="C170">
-        <v>96.160929338251</v>
+        <v>96.8910158087285</v>
       </c>
       <c r="D170">
         <v>3.65536536517558</v>
@@ -2753,10 +2753,10 @@
         <v>2005-08</v>
       </c>
       <c r="B171">
-        <v>103.869375780369</v>
+        <v>103.218427391081</v>
       </c>
       <c r="C171">
-        <v>98.7366843878715</v>
+        <v>99.5442693078722</v>
       </c>
       <c r="D171">
         <v>3.73686102808308</v>
@@ -2767,10 +2767,10 @@
         <v>2005-09</v>
       </c>
       <c r="B172">
-        <v>105.791693401992</v>
+        <v>105.455252906428</v>
       </c>
       <c r="C172">
-        <v>99.2959698661373</v>
+        <v>100.39945085127</v>
       </c>
       <c r="D172">
         <v>3.81692023815057</v>
@@ -2781,10 +2781,10 @@
         <v>2005-10</v>
       </c>
       <c r="B173">
-        <v>106.98612038889</v>
+        <v>106.382223037743</v>
       </c>
       <c r="C173">
-        <v>100.744832144792</v>
+        <v>101.949670450306</v>
       </c>
       <c r="D173">
         <v>3.89557354570562</v>
@@ -2795,10 +2795,10 @@
         <v>2005-11</v>
       </c>
       <c r="B174">
-        <v>107.528749646629</v>
+        <v>107.432722181557</v>
       </c>
       <c r="C174">
-        <v>100.905839830313</v>
+        <v>101.977350093363</v>
       </c>
       <c r="D174">
         <v>3.99353652582045</v>
@@ -2809,10 +2809,10 @@
         <v>2005-12</v>
       </c>
       <c r="B175">
-        <v>109.740673185047</v>
+        <v>109.766422434904</v>
       </c>
       <c r="C175">
-        <v>102.949212196168</v>
+        <v>103.603473164327</v>
       </c>
       <c r="D175">
         <v>4.11058640096404</v>
@@ -2823,10 +2823,10 @@
         <v>2006-01</v>
       </c>
       <c r="B176">
-        <v>110.652584306168</v>
+        <v>110.748434589583</v>
       </c>
       <c r="C176">
-        <v>103.126951930928</v>
+        <v>103.803091685739</v>
       </c>
       <c r="D176">
         <v>4.24647744242317</v>
@@ -2837,10 +2837,10 @@
         <v>2006-02</v>
       </c>
       <c r="B177">
-        <v>110.728457489283</v>
+        <v>111.360952883491</v>
       </c>
       <c r="C177">
-        <v>103.480653721509</v>
+        <v>104.711182872212</v>
       </c>
       <c r="D177">
         <v>4.331422420895</v>
@@ -2851,10 +2851,10 @@
         <v>2006-03</v>
       </c>
       <c r="B178">
-        <v>110.146037189688</v>
+        <v>110.734259441741</v>
       </c>
       <c r="C178">
-        <v>102.923380586027</v>
+        <v>104.267009146781</v>
       </c>
       <c r="D178">
         <v>4.36590435240225</v>
@@ -2865,10 +2865,10 @@
         <v>2006-04</v>
       </c>
       <c r="B179">
-        <v>109.928860817923</v>
+        <v>109.778079756424</v>
       </c>
       <c r="C179">
-        <v>104.316314267993</v>
+        <v>105.397889205627</v>
       </c>
       <c r="D179">
         <v>4.35038709062525</v>
@@ -2879,10 +2879,10 @@
         <v>2006-05</v>
       </c>
       <c r="B180">
-        <v>111.902418326295</v>
+        <v>112.691893913538</v>
       </c>
       <c r="C180">
-        <v>106.393591159352</v>
+        <v>107.23369794001</v>
       </c>
       <c r="D180">
         <v>4.28439285088984</v>
@@ -2893,10 +2893,10 @@
         <v>2006-06</v>
       </c>
       <c r="B181">
-        <v>111.643767300268</v>
+        <v>112.11140773427</v>
       </c>
       <c r="C181">
-        <v>107.503385145268</v>
+        <v>107.949038369744</v>
       </c>
       <c r="D181">
         <v>4.16844247175219</v>
@@ -2907,10 +2907,10 @@
         <v>2006-07</v>
       </c>
       <c r="B182">
-        <v>109.903666911186</v>
+        <v>109.783935217009</v>
       </c>
       <c r="C182">
-        <v>106.591697150408</v>
+        <v>107.746201035398</v>
       </c>
       <c r="D182">
         <v>4.00311066791257</v>
@@ -2921,10 +2921,10 @@
         <v>2006-08</v>
       </c>
       <c r="B183">
-        <v>107.344001165674</v>
+        <v>107.350297430865</v>
       </c>
       <c r="C183">
-        <v>103.477050102691</v>
+        <v>104.660207908964</v>
       </c>
       <c r="D183">
         <v>3.94412044810444</v>
@@ -2935,10 +2935,10 @@
         <v>2006-09</v>
       </c>
       <c r="B184">
-        <v>107.847379139467</v>
+        <v>108.234683797269</v>
       </c>
       <c r="C184">
-        <v>102.478804471597</v>
+        <v>104.577441416027</v>
       </c>
       <c r="D184">
         <v>3.990354361822</v>
@@ -2949,10 +2949,10 @@
         <v>2006-10</v>
       </c>
       <c r="B185">
-        <v>107.867440627361</v>
+        <v>108.63844758809</v>
       </c>
       <c r="C185">
-        <v>103.542189226854</v>
+        <v>105.416460322565</v>
       </c>
       <c r="D185">
         <v>4.1407671767584</v>
@@ -2963,10 +2963,10 @@
         <v>2006-11</v>
       </c>
       <c r="B186">
-        <v>111.740932910906</v>
+        <v>111.754029625222</v>
       </c>
       <c r="C186">
-        <v>106.244071774788</v>
+        <v>107.476121256046</v>
       </c>
       <c r="D186">
         <v>4.21828442530365</v>
@@ -2977,10 +2977,10 @@
         <v>2006-12</v>
       </c>
       <c r="B187">
-        <v>112.575293434389</v>
+        <v>113.138337171194</v>
       </c>
       <c r="C187">
-        <v>107.384468861456</v>
+        <v>108.829392863369</v>
       </c>
       <c r="D187">
         <v>4.22360793296752</v>
@@ -2991,10 +2991,10 @@
         <v>2007-01</v>
       </c>
       <c r="B188">
-        <v>112.410364802009</v>
+        <v>112.575737259219</v>
       </c>
       <c r="C188">
-        <v>107.160989943966</v>
+        <v>108.689853613935</v>
       </c>
       <c r="D188">
         <v>4.15760618135383</v>
@@ -3005,10 +3005,10 @@
         <v>2007-02</v>
       </c>
       <c r="B189">
-        <v>112.045553963753</v>
+        <v>112.139627638836</v>
       </c>
       <c r="C189">
-        <v>106.111941515705</v>
+        <v>108.323753224019</v>
       </c>
       <c r="D189">
         <v>4.13823342452551</v>
@@ -3019,10 +3019,10 @@
         <v>2007-03</v>
       </c>
       <c r="B190">
-        <v>111.982464018307</v>
+        <v>112.180522691672</v>
       </c>
       <c r="C190">
-        <v>106.149803543023</v>
+        <v>107.749285615225</v>
       </c>
       <c r="D190">
         <v>4.16491444150854</v>
@@ -3033,10 +3033,10 @@
         <v>2007-04</v>
       </c>
       <c r="B191">
-        <v>110.559599183017</v>
+        <v>110.877608560316</v>
       </c>
       <c r="C191">
-        <v>106.256797251217</v>
+        <v>108.00233026698</v>
       </c>
       <c r="D191">
         <v>4.23722629898506</v>
@@ -3047,10 +3047,10 @@
         <v>2007-05</v>
       </c>
       <c r="B192">
-        <v>108.690292774182</v>
+        <v>108.350828163941</v>
       </c>
       <c r="C192">
-        <v>103.324583265624</v>
+        <v>104.968757872048</v>
       </c>
       <c r="D192">
         <v>4.27940773633118</v>
@@ -3061,10 +3061,10 @@
         <v>2007-06</v>
       </c>
       <c r="B193">
-        <v>107.544238721362</v>
+        <v>107.44665630914</v>
       </c>
       <c r="C193">
-        <v>101.379677705322</v>
+        <v>102.464905154807</v>
       </c>
       <c r="D193">
         <v>4.29172454491966</v>
@@ -3075,10 +3075,10 @@
         <v>2007-07</v>
       </c>
       <c r="B194">
-        <v>108.745498573362</v>
+        <v>109.656289324833</v>
       </c>
       <c r="C194">
-        <v>102.312544075244</v>
+        <v>103.918420869881</v>
       </c>
       <c r="D194">
         <v>4.2743898273647</v>
@@ -3089,10 +3089,10 @@
         <v>2007-08</v>
       </c>
       <c r="B195">
-        <v>109.04815504947</v>
+        <v>109.65469895403</v>
       </c>
       <c r="C195">
-        <v>103.025389629163</v>
+        <v>104.43489284498</v>
       </c>
       <c r="D195">
         <v>4.2531799822715</v>
@@ -3103,10 +3103,10 @@
         <v>2007-09</v>
       </c>
       <c r="B196">
-        <v>108.590092099926</v>
+        <v>107.635872659875</v>
       </c>
       <c r="C196">
-        <v>103.798243252301</v>
+        <v>105.071057272804</v>
       </c>
       <c r="D196">
         <v>4.22818695149529</v>
@@ -3117,10 +3117,10 @@
         <v>2007-10</v>
       </c>
       <c r="B197">
-        <v>108.822057567102</v>
+        <v>109.550280883138</v>
       </c>
       <c r="C197">
-        <v>102.534352725544</v>
+        <v>104.674111676268</v>
       </c>
       <c r="D197">
         <v>4.19952217831946</v>
@@ -3131,10 +3131,10 @@
         <v>2007-11</v>
       </c>
       <c r="B198">
-        <v>106.563937501324</v>
+        <v>107.340778221041</v>
       </c>
       <c r="C198">
-        <v>100.209511419386</v>
+        <v>102.580044132727</v>
       </c>
       <c r="D198">
         <v>4.09747416994726</v>
@@ -3145,10 +3145,10 @@
         <v>2007-12</v>
       </c>
       <c r="B199">
-        <v>107.008843649898</v>
+        <v>106.871047444245</v>
       </c>
       <c r="C199">
-        <v>101.665966575931</v>
+        <v>103.973041793309</v>
       </c>
       <c r="D199">
         <v>3.9229238463611</v>
@@ -3159,10 +3159,10 @@
         <v>2008-01</v>
       </c>
       <c r="B200">
-        <v>104.194884758343</v>
+        <v>104.893023070423</v>
       </c>
       <c r="C200">
-        <v>100.682761978612</v>
+        <v>102.57520868387</v>
       </c>
       <c r="D200">
         <v>3.67661781354354</v>
@@ -3173,10 +3173,10 @@
         <v>2008-02</v>
       </c>
       <c r="B201">
-        <v>102.288514886207</v>
+        <v>102.674548824697</v>
       </c>
       <c r="C201">
-        <v>96.7580427799815</v>
+        <v>99.2671464487604</v>
       </c>
       <c r="D201">
         <v>3.44006334812379</v>
@@ -3187,10 +3187,10 @@
         <v>2008-03</v>
       </c>
       <c r="B202">
-        <v>100.083286670791</v>
+        <v>99.947729356618</v>
       </c>
       <c r="C202">
-        <v>96.1620010801833</v>
+        <v>98.3098852890374</v>
       </c>
       <c r="D202">
         <v>3.21309407516419</v>
@@ -3201,10 +3201,10 @@
         <v>2008-04</v>
       </c>
       <c r="B203">
-        <v>99.768228157954</v>
+        <v>100.263796101521</v>
       </c>
       <c r="C203">
-        <v>95.3493904179973</v>
+        <v>97.0097207532091</v>
       </c>
       <c r="D203">
         <v>2.99555072485443</v>
@@ -3215,10 +3215,10 @@
         <v>2008-05</v>
       </c>
       <c r="B204">
-        <v>96.8676144955994</v>
+        <v>97.4125850219906</v>
       </c>
       <c r="C204">
-        <v>91.9489606582695</v>
+        <v>93.5637864458573</v>
       </c>
       <c r="D204">
         <v>2.78592592740799</v>
@@ -3229,10 +3229,10 @@
         <v>2008-06</v>
       </c>
       <c r="B205">
-        <v>92.7006185848632</v>
+        <v>92.3381808091123</v>
       </c>
       <c r="C205">
-        <v>90.1835592201885</v>
+        <v>91.6783892231233</v>
       </c>
       <c r="D205">
         <v>2.58379446344725</v>
@@ -3243,10 +3243,10 @@
         <v>2008-07</v>
       </c>
       <c r="B206">
-        <v>92.0140548726495</v>
+        <v>91.956275202677</v>
       </c>
       <c r="C206">
-        <v>88.048282011055</v>
+        <v>89.5293882500279</v>
       </c>
       <c r="D206">
         <v>2.3887609865079</v>
@@ -3257,10 +3257,10 @@
         <v>2008-08</v>
       </c>
       <c r="B207">
-        <v>87.7429142285478</v>
+        <v>87.7789636504219</v>
       </c>
       <c r="C207">
-        <v>85.8162025389532</v>
+        <v>87.697402152432</v>
       </c>
       <c r="D207">
         <v>1.92886486996208</v>
@@ -3271,10 +3271,10 @@
         <v>2008-09</v>
       </c>
       <c r="B208">
-        <v>85.0312311534026</v>
+        <v>85.3684123488384</v>
       </c>
       <c r="C208">
-        <v>85.2136083573278</v>
+        <v>86.9701095776548</v>
       </c>
       <c r="D208">
         <v>1.20745448825197</v>
@@ -3285,10 +3285,10 @@
         <v>2008-10</v>
       </c>
       <c r="B209">
-        <v>83.4360456282714</v>
+        <v>83.4946221006201</v>
       </c>
       <c r="C209">
-        <v>82.6691047799831</v>
+        <v>83.9347904597705</v>
       </c>
       <c r="D209">
         <v>0.229211153319881</v>
@@ -3299,10 +3299,10 @@
         <v>2008-11</v>
       </c>
       <c r="B210">
-        <v>68.4198307692063</v>
+        <v>67.4098244390232</v>
       </c>
       <c r="C210">
-        <v>69.2004876520677</v>
+        <v>70.050290750257</v>
       </c>
       <c r="D210">
         <v>-0.72759216622039</v>
@@ -3313,10 +3313,10 @@
         <v>2008-12</v>
       </c>
       <c r="B211">
-        <v>55.7607737878649</v>
+        <v>54.0266835148937</v>
       </c>
       <c r="C211">
-        <v>55.4044041106592</v>
+        <v>57.492094573654</v>
       </c>
       <c r="D211">
         <v>-1.66599408127644</v>
@@ -3327,10 +3327,10 @@
         <v>2009-01</v>
       </c>
       <c r="B212">
-        <v>53.007625370091</v>
+        <v>53.1407591796117</v>
       </c>
       <c r="C212">
-        <v>52.1975928773311</v>
+        <v>53.9431611410266</v>
       </c>
       <c r="D212">
         <v>-2.58888941022897</v>
@@ -3341,10 +3341,10 @@
         <v>2009-02</v>
       </c>
       <c r="B213">
-        <v>53.0284558395345</v>
+        <v>52.0994185467978</v>
       </c>
       <c r="C213">
-        <v>56.8073092719408</v>
+        <v>58.2490133593483</v>
       </c>
       <c r="D213">
         <v>-3.0717211625178</v>
@@ -3355,10 +3355,10 @@
         <v>2009-03</v>
       </c>
       <c r="B214">
-        <v>54.8669269032643</v>
+        <v>53.6691250867356</v>
       </c>
       <c r="C214">
-        <v>61.6287167692353</v>
+        <v>63.1278144346816</v>
       </c>
       <c r="D214">
         <v>-3.11640181323197</v>
@@ -3369,10 +3369,10 @@
         <v>2009-04</v>
       </c>
       <c r="B215">
-        <v>59.645597873059</v>
+        <v>60.1061992495978</v>
       </c>
       <c r="C215">
-        <v>64.4389875367904</v>
+        <v>65.4067360488145</v>
       </c>
       <c r="D215">
         <v>-2.72481798921351</v>
@@ -3383,10 +3383,10 @@
         <v>2009-05</v>
       </c>
       <c r="B216">
-        <v>67.6450383820352</v>
+        <v>67.8848362280176</v>
       </c>
       <c r="C216">
-        <v>77.5556447721392</v>
+        <v>79.2680171669472</v>
       </c>
       <c r="D216">
         <v>-2.3802994791686</v>
@@ -3397,10 +3397,10 @@
         <v>2009-06</v>
       </c>
       <c r="B217">
-        <v>73.6797658273041</v>
+        <v>76.1954998165979</v>
       </c>
       <c r="C217">
-        <v>84.9608334002492</v>
+        <v>85.7839263047654</v>
       </c>
       <c r="D217">
         <v>-2.08219530634206</v>
@@ -3411,10 +3411,10 @@
         <v>2009-07</v>
       </c>
       <c r="B218">
-        <v>81.1816278177557</v>
+        <v>81.2309083601056</v>
       </c>
       <c r="C218">
-        <v>91.7297992844034</v>
+        <v>93.0847377856961</v>
       </c>
       <c r="D218">
         <v>-1.82999652426383</v>
@@ -3425,10 +3425,10 @@
         <v>2009-08</v>
       </c>
       <c r="B219">
-        <v>87.334851307566</v>
+        <v>87.9989346776156</v>
       </c>
       <c r="C219">
-        <v>97.0453390888278</v>
+        <v>97.3629357974664</v>
       </c>
       <c r="D219">
         <v>-1.33711339219019</v>
@@ -3439,10 +3439,10 @@
         <v>2009-09</v>
       </c>
       <c r="B220">
-        <v>94.7082145802871</v>
+        <v>97.0132911776238</v>
       </c>
       <c r="C220">
-        <v>101.866221797819</v>
+        <v>102.394585167581</v>
       </c>
       <c r="D220">
         <v>-0.599686316537785</v>
@@ -3453,10 +3453,10 @@
         <v>2009-10</v>
       </c>
       <c r="B221">
-        <v>95.241862188912</v>
+        <v>95.6156140263425</v>
       </c>
       <c r="C221">
-        <v>102.846341497037</v>
+        <v>103.689665255228</v>
       </c>
       <c r="D221">
         <v>0.388731863047326</v>
@@ -3467,10 +3467,10 @@
         <v>2009-11</v>
       </c>
       <c r="B222">
-        <v>103.510026514825</v>
+        <v>104.615608500483</v>
       </c>
       <c r="C222">
-        <v>113.804803273565</v>
+        <v>113.578441434716</v>
       </c>
       <c r="D222">
         <v>1.41260221098432</v>
@@ -3481,10 +3481,10 @@
         <v>2009-12</v>
       </c>
       <c r="B223">
-        <v>108.429123421979</v>
+        <v>111.174750840398</v>
       </c>
       <c r="C223">
-        <v>118.777210060073</v>
+        <v>116.123442036337</v>
       </c>
       <c r="D223">
         <v>2.475231786885</v>
@@ -3495,10 +3495,10 @@
         <v>2010-01</v>
       </c>
       <c r="B224">
-        <v>113.317390511791</v>
+        <v>113.320547592094</v>
       </c>
       <c r="C224">
-        <v>122.730875399872</v>
+        <v>122.466772951962</v>
       </c>
       <c r="D224">
         <v>3.58021824164803</v>
@@ -3509,10 +3509,10 @@
         <v>2010-02</v>
       </c>
       <c r="B225">
-        <v>115.26891403961</v>
+        <v>115.475146967681</v>
       </c>
       <c r="C225">
-        <v>122.959106586076</v>
+        <v>123.905832504163</v>
       </c>
       <c r="D225">
         <v>4.30721280370511</v>
@@ -3523,10 +3523,10 @@
         <v>2010-03</v>
       </c>
       <c r="B226">
-        <v>115.306934528768</v>
+        <v>116.176880716149</v>
       </c>
       <c r="C226">
-        <v>120.339618455245</v>
+        <v>121.765677256827</v>
       </c>
       <c r="D226">
         <v>4.64239711702361</v>
@@ -3537,10 +3537,10 @@
         <v>2010-04</v>
       </c>
       <c r="B227">
-        <v>117.476768053725</v>
+        <v>117.755098386787</v>
       </c>
       <c r="C227">
-        <v>123.23823756469</v>
+        <v>124.670874944529</v>
       </c>
       <c r="D227">
         <v>4.58240967669177</v>
@@ -3551,10 +3551,10 @@
         <v>2010-05</v>
       </c>
       <c r="B228">
-        <v>118.064078787505</v>
+        <v>117.881836912865</v>
       </c>
       <c r="C228">
-        <v>121.582702944048</v>
+        <v>122.821223447081</v>
       </c>
       <c r="D228">
         <v>4.5692210806523</v>
@@ -3565,10 +3565,10 @@
         <v>2010-06</v>
       </c>
       <c r="B229">
-        <v>119.387634857292</v>
+        <v>118.376406674652</v>
       </c>
       <c r="C229">
-        <v>119.699485955589</v>
+        <v>121.85427862626</v>
       </c>
       <c r="D229">
         <v>4.60217032274409</v>
@@ -3579,10 +3579,10 @@
         <v>2010-07</v>
       </c>
       <c r="B230">
-        <v>114.357049688254</v>
+        <v>114.533466736724</v>
       </c>
       <c r="C230">
-        <v>114.672820963864</v>
+        <v>116.066196222301</v>
       </c>
       <c r="D230">
         <v>4.68087506362713</v>
@@ -3593,10 +3593,10 @@
         <v>2010-08</v>
       </c>
       <c r="B231">
-        <v>112.177904721871</v>
+        <v>112.056808800221</v>
       </c>
       <c r="C231">
-        <v>110.477019581186</v>
+        <v>112.357252285309</v>
       </c>
       <c r="D231">
         <v>4.69761295533139</v>
@@ -3607,10 +3607,10 @@
         <v>2010-09</v>
       </c>
       <c r="B232">
-        <v>108.849839371992</v>
+        <v>108.102736961576</v>
       </c>
       <c r="C232">
-        <v>106.605118128407</v>
+        <v>107.898314525594</v>
       </c>
       <c r="D232">
         <v>4.65294048173313</v>
@@ -3621,10 +3621,10 @@
         <v>2010-10</v>
       </c>
       <c r="B233">
-        <v>110.030038806657</v>
+        <v>109.797297412407</v>
       </c>
       <c r="C233">
-        <v>107.595294971511</v>
+        <v>109.755190859652</v>
       </c>
       <c r="D233">
         <v>4.54767046901929</v>
@@ -3635,10 +3635,10 @@
         <v>2010-11</v>
       </c>
       <c r="B234">
-        <v>109.250193776404</v>
+        <v>109.491313035862</v>
       </c>
       <c r="C234">
-        <v>106.297732880366</v>
+        <v>108.556177665613</v>
       </c>
       <c r="D234">
         <v>4.46917533155053</v>
@@ -3649,10 +3649,10 @@
         <v>2010-12</v>
       </c>
       <c r="B235">
-        <v>112.993193690754</v>
+        <v>112.535196857658</v>
       </c>
       <c r="C235">
-        <v>109.392717141502</v>
+        <v>111.697492961946</v>
       </c>
       <c r="D235">
         <v>4.41699351019864</v>
@@ -3663,10 +3663,10 @@
         <v>2011-01</v>
       </c>
       <c r="B236">
-        <v>112.319415602012</v>
+        <v>113.126389820307</v>
       </c>
       <c r="C236">
-        <v>107.242860615305</v>
+        <v>110.093259729237</v>
       </c>
       <c r="D236">
         <v>4.39076575833917</v>
@@ -3677,10 +3677,10 @@
         <v>2011-02</v>
       </c>
       <c r="B237">
-        <v>110.155384389958</v>
+        <v>110.8902354029</v>
       </c>
       <c r="C237">
-        <v>105.63711856998</v>
+        <v>107.938444507345</v>
       </c>
       <c r="D237">
         <v>4.28642678642983</v>
@@ -3691,10 +3691,10 @@
         <v>2011-03</v>
       </c>
       <c r="B238">
-        <v>112.443313793579</v>
+        <v>113.181076942974</v>
       </c>
       <c r="C238">
-        <v>107.165019629969</v>
+        <v>109.053964296388</v>
       </c>
       <c r="D238">
         <v>4.10501236072569</v>
@@ -3705,10 +3705,10 @@
         <v>2011-04</v>
       </c>
       <c r="B239">
-        <v>107.486011249283</v>
+        <v>108.141878188213</v>
       </c>
       <c r="C239">
-        <v>102.890688938047</v>
+        <v>104.185416785174</v>
       </c>
       <c r="D239">
         <v>3.84787663999479</v>
@@ -3719,10 +3719,10 @@
         <v>2011-05</v>
       </c>
       <c r="B240">
-        <v>101.902977729666</v>
+        <v>103.751508545196</v>
       </c>
       <c r="C240">
-        <v>96.105463515566</v>
+        <v>97.9446455986152</v>
       </c>
       <c r="D240">
         <v>3.6430077960851</v>
@@ -3733,10 +3733,10 @@
         <v>2011-06</v>
       </c>
       <c r="B241">
-        <v>99.7863832921728</v>
+        <v>100.043033944443</v>
       </c>
       <c r="C241">
-        <v>97.4557843330346</v>
+        <v>99.2861936206154</v>
       </c>
       <c r="D241">
         <v>3.48940396260036</v>
@@ -3747,10 +3747,10 @@
         <v>2011-07</v>
       </c>
       <c r="B242">
-        <v>98.3462943352411</v>
+        <v>98.9127770229984</v>
       </c>
       <c r="C242">
-        <v>98.3822013566346</v>
+        <v>99.5435106149255</v>
       </c>
       <c r="D242">
         <v>3.38624223769213</v>
@@ -3761,10 +3761,10 @@
         <v>2011-08</v>
       </c>
       <c r="B243">
-        <v>98.0066623096182</v>
+        <v>98.3871344496887</v>
       </c>
       <c r="C243">
-        <v>99.9681574876289</v>
+        <v>102.22512105293</v>
       </c>
       <c r="D243">
         <v>3.26493376280168</v>
@@ -3775,10 +3775,10 @@
         <v>2011-09</v>
       </c>
       <c r="B244">
-        <v>97.0699575401859</v>
+        <v>96.6703191678739</v>
       </c>
       <c r="C244">
-        <v>99.6610592843355</v>
+        <v>101.303541919199</v>
       </c>
       <c r="D244">
         <v>3.12570994650547</v>
@@ -3789,10 +3789,10 @@
         <v>2011-10</v>
       </c>
       <c r="B245">
-        <v>95.0520528324774</v>
+        <v>95.6977834574563</v>
       </c>
       <c r="C245">
-        <v>96.6375629751777</v>
+        <v>98.6459973893895</v>
       </c>
       <c r="D245">
         <v>2.96881350689169</v>
@@ -3803,10 +3803,10 @@
         <v>2011-11</v>
       </c>
       <c r="B246">
-        <v>94.5136512694134</v>
+        <v>95.2227040301468</v>
       </c>
       <c r="C246">
-        <v>93.3656958704033</v>
+        <v>96.0190498043954</v>
       </c>
       <c r="D246">
         <v>2.92612277682861</v>
@@ -3817,10 +3817,10 @@
         <v>2011-12</v>
       </c>
       <c r="B247">
-        <v>92.9794581556836</v>
+        <v>93.3941718095231</v>
       </c>
       <c r="C247">
-        <v>91.0436673710161</v>
+        <v>93.2098526555076</v>
       </c>
       <c r="D247">
         <v>2.99648748896952</v>
@@ -3831,10 +3831,10 @@
         <v>2012-01</v>
       </c>
       <c r="B248">
-        <v>92.861366891764</v>
+        <v>94.3975099915076</v>
       </c>
       <c r="C248">
-        <v>91.3846571350247</v>
+        <v>93.5393122740236</v>
       </c>
       <c r="D248">
         <v>3.17901546651522</v>
@@ -3845,10 +3845,10 @@
         <v>2012-02</v>
       </c>
       <c r="B249">
-        <v>92.7669084724002</v>
+        <v>93.7236809726242</v>
       </c>
       <c r="C249">
-        <v>90.9792848066878</v>
+        <v>93.0618426356599</v>
       </c>
       <c r="D249">
         <v>3.24993638574999</v>
@@ -3859,10 +3859,10 @@
         <v>2012-03</v>
       </c>
       <c r="B250">
-        <v>96.5021522009617</v>
+        <v>96.6139814585233</v>
       </c>
       <c r="C250">
-        <v>92.9731889919256</v>
+        <v>95.315830455092</v>
       </c>
       <c r="D250">
         <v>3.21007886794666</v>
@@ -3873,10 +3873,10 @@
         <v>2012-04</v>
       </c>
       <c r="B251">
-        <v>97.4325140196093</v>
+        <v>98.0643530651073</v>
       </c>
       <c r="C251">
-        <v>94.9310454231579</v>
+        <v>96.1856412166292</v>
       </c>
       <c r="D251">
         <v>3.06024969268333</v>
@@ -3887,10 +3887,10 @@
         <v>2012-05</v>
       </c>
       <c r="B252">
-        <v>96.198041303331</v>
+        <v>96.9823704668264</v>
       </c>
       <c r="C252">
-        <v>95.3111754886561</v>
+        <v>96.8348787962568</v>
       </c>
       <c r="D252">
         <v>2.95326117861609</v>
@@ -3901,10 +3901,10 @@
         <v>2012-06</v>
       </c>
       <c r="B253">
-        <v>92.8206401028395</v>
+        <v>94.7619307412437</v>
       </c>
       <c r="C253">
-        <v>91.7963980409305</v>
+        <v>93.2610852133475</v>
       </c>
       <c r="D253">
         <v>2.8887943687516</v>
@@ -3915,10 +3915,10 @@
         <v>2012-07</v>
       </c>
       <c r="B254">
-        <v>92.2978959829816</v>
+        <v>93.7446948518716</v>
       </c>
       <c r="C254">
-        <v>89.1212646064309</v>
+        <v>91.8495902464756</v>
       </c>
       <c r="D254">
         <v>2.86654662383721</v>
@@ -3929,10 +3929,10 @@
         <v>2012-08</v>
       </c>
       <c r="B255">
-        <v>88.5830538021981</v>
+        <v>90.3984094955788</v>
       </c>
       <c r="C255">
-        <v>88.5376198448463</v>
+        <v>91.6115039768755</v>
       </c>
       <c r="D255">
         <v>2.82339768188</v>
@@ -3943,10 +3943,10 @@
         <v>2012-09</v>
       </c>
       <c r="B256">
-        <v>89.6127234724511</v>
+        <v>90.8407323343284</v>
       </c>
       <c r="C256">
-        <v>89.6899188861501</v>
+        <v>91.9915306341946</v>
       </c>
       <c r="D256">
         <v>2.75947848606467</v>
@@ -3957,10 +3957,10 @@
         <v>2012-10</v>
       </c>
       <c r="B257">
-        <v>89.3466424893007</v>
+        <v>89.8200613953728</v>
       </c>
       <c r="C257">
-        <v>91.3974936492528</v>
+        <v>92.5265808654044</v>
       </c>
       <c r="D257">
         <v>2.67491305841099</v>
@@ -3971,10 +3971,10 @@
         <v>2012-11</v>
       </c>
       <c r="B258">
-        <v>86.4926630802304</v>
+        <v>86.6588575257095</v>
       </c>
       <c r="C258">
-        <v>91.9098678143388</v>
+        <v>92.0903428271907</v>
       </c>
       <c r="D258">
         <v>2.5899370070269</v>
@@ -3985,10 +3985,10 @@
         <v>2012-12</v>
       </c>
       <c r="B259">
-        <v>86.6357320587141</v>
+        <v>86.109401600209</v>
       </c>
       <c r="C259">
-        <v>94.3049551382767</v>
+        <v>94.7997758263869</v>
       </c>
       <c r="D259">
         <v>2.50474105958168</v>
@@ -3999,10 +3999,10 @@
         <v>2013-01</v>
       </c>
       <c r="B260">
-        <v>89.4334215971842</v>
+        <v>89.196256901354</v>
       </c>
       <c r="C260">
-        <v>96.4283560015804</v>
+        <v>96.9500333620559</v>
       </c>
       <c r="D260">
         <v>2.41951449647135</v>
@@ -4013,10 +4013,10 @@
         <v>2013-02</v>
       </c>
       <c r="B261">
-        <v>91.9585906615778</v>
+        <v>91.1531707887025</v>
       </c>
       <c r="C261">
-        <v>101.305386712799</v>
+        <v>102.361672179612</v>
       </c>
       <c r="D261">
         <v>2.42508896956979</v>
@@ -4027,10 +4027,10 @@
         <v>2013-03</v>
       </c>
       <c r="B262">
-        <v>92.6962871128359</v>
+        <v>92.9486423301324</v>
       </c>
       <c r="C262">
-        <v>101.005116605779</v>
+        <v>102.385453741636</v>
       </c>
       <c r="D262">
         <v>2.52062563357727</v>
@@ -4041,10 +4041,10 @@
         <v>2013-04</v>
       </c>
       <c r="B263">
-        <v>95.0950584111967</v>
+        <v>94.7455450572108</v>
       </c>
       <c r="C263">
-        <v>102.670534838883</v>
+        <v>103.752486506638</v>
       </c>
       <c r="D263">
         <v>2.70588251744435</v>
@@ -4055,10 +4055,10 @@
         <v>2013-05</v>
       </c>
       <c r="B264">
-        <v>92.8400938644464</v>
+        <v>92.5759571592512</v>
       </c>
       <c r="C264">
-        <v>99.8649730718933</v>
+        <v>100.468730334956</v>
       </c>
       <c r="D264">
         <v>2.87231162085529</v>
@@ -4069,10 +4069,10 @@
         <v>2013-06</v>
       </c>
       <c r="B265">
-        <v>97.1287292823025</v>
+        <v>96.4253894358253</v>
       </c>
       <c r="C265">
-        <v>102.824664492706</v>
+        <v>102.715933216179</v>
       </c>
       <c r="D265">
         <v>3.01980962716155</v>
@@ -4083,10 +4083,10 @@
         <v>2013-07</v>
       </c>
       <c r="B266">
-        <v>98.5238952403414</v>
+        <v>98.4092141794041</v>
       </c>
       <c r="C266">
-        <v>105.635907171424</v>
+        <v>105.485032569384</v>
       </c>
       <c r="D266">
         <v>3.14831418368304</v>
@@ -4097,10 +4097,10 @@
         <v>2013-08</v>
       </c>
       <c r="B267">
-        <v>100.178494824304</v>
+        <v>99.9132640195986</v>
       </c>
       <c r="C267">
-        <v>105.585557844784</v>
+        <v>105.229529813925</v>
       </c>
       <c r="D267">
         <v>3.29084217484805</v>
@@ -4111,10 +4111,10 @@
         <v>2013-09</v>
       </c>
       <c r="B268">
-        <v>104.161079038012</v>
+        <v>103.081604285293</v>
       </c>
       <c r="C268">
-        <v>108.083749005815</v>
+        <v>108.065398275092</v>
       </c>
       <c r="D268">
         <v>3.44742635955441</v>
@@ -4125,10 +4125,10 @@
         <v>2013-10</v>
       </c>
       <c r="B269">
-        <v>104.817753301116</v>
+        <v>104.983919210827</v>
       </c>
       <c r="C269">
-        <v>108.403821981905</v>
+        <v>108.127019692108</v>
       </c>
       <c r="D269">
         <v>3.6181203848062</v>
@@ -4139,10 +4139,10 @@
         <v>2013-11</v>
       </c>
       <c r="B270">
-        <v>106.493420063684</v>
+        <v>106.272016366521</v>
       </c>
       <c r="C270">
-        <v>109.861046311514</v>
+        <v>110.086282917969</v>
       </c>
       <c r="D270">
         <v>3.68728507841485</v>
@@ -4153,10 +4153,10 @@
         <v>2013-12</v>
       </c>
       <c r="B271">
-        <v>106.933959419121</v>
+        <v>107.052241000166</v>
       </c>
       <c r="C271">
-        <v>109.634969318187</v>
+        <v>109.902131717521</v>
       </c>
       <c r="D271">
         <v>3.65537460300722</v>
@@ -4167,10 +4167,10 @@
         <v>2014-01</v>
       </c>
       <c r="B272">
-        <v>105.572597844316</v>
+        <v>105.248745037086</v>
       </c>
       <c r="C272">
-        <v>108.259800718924</v>
+        <v>108.188137319792</v>
       </c>
       <c r="D272">
         <v>3.52327872168973</v>
@@ -4181,10 +4181,10 @@
         <v>2014-02</v>
       </c>
       <c r="B273">
-        <v>107.406086359188</v>
+        <v>107.839743813444</v>
       </c>
       <c r="C273">
-        <v>107.726163674759</v>
+        <v>106.96601014552</v>
       </c>
       <c r="D273">
         <v>3.4425289870575</v>
@@ -4195,10 +4195,10 @@
         <v>2014-03</v>
       </c>
       <c r="B274">
-        <v>105.177636145407</v>
+        <v>105.301604726191</v>
       </c>
       <c r="C274">
-        <v>106.295184634414</v>
+        <v>106.443868928786</v>
       </c>
       <c r="D274">
         <v>3.41258152577548</v>
@@ -4209,10 +4209,10 @@
         <v>2014-04</v>
       </c>
       <c r="B275">
-        <v>103.206630482251</v>
+        <v>103.301894747473</v>
       </c>
       <c r="C275">
-        <v>102.792728124554</v>
+        <v>103.006665430017</v>
       </c>
       <c r="D275">
         <v>3.43296357782796</v>
@@ -4223,10 +4223,10 @@
         <v>2014-05</v>
       </c>
       <c r="B276">
-        <v>105.831720360216</v>
+        <v>104.927980577115</v>
       </c>
       <c r="C276">
-        <v>103.614053656354</v>
+        <v>104.247803419662</v>
       </c>
       <c r="D276">
         <v>3.44747842134572</v>
@@ -4237,10 +4237,10 @@
         <v>2014-06</v>
       </c>
       <c r="B277">
-        <v>104.290966274524</v>
+        <v>104.204458366901</v>
       </c>
       <c r="C277">
-        <v>103.677166672762</v>
+        <v>104.262030756561</v>
       </c>
       <c r="D277">
         <v>3.45616987207119</v>
@@ -4251,10 +4251,10 @@
         <v>2014-07</v>
       </c>
       <c r="B278">
-        <v>103.913802430377</v>
+        <v>103.395269460032</v>
       </c>
       <c r="C278">
-        <v>103.211161979843</v>
+        <v>103.177251770594</v>
       </c>
       <c r="D278">
         <v>3.45908736575254</v>
@@ -4265,10 +4265,10 @@
         <v>2014-08</v>
       </c>
       <c r="B279">
-        <v>105.341285347672</v>
+        <v>104.768873638335</v>
       </c>
       <c r="C279">
-        <v>104.898362413972</v>
+        <v>104.92509156502</v>
       </c>
       <c r="D279">
         <v>3.43161878429561</v>
@@ -4279,10 +4279,10 @@
         <v>2014-09</v>
       </c>
       <c r="B280">
-        <v>103.270295844169</v>
+        <v>103.991007379875</v>
       </c>
       <c r="C280">
-        <v>103.211144793058</v>
+        <v>103.15785132566</v>
       </c>
       <c r="D280">
         <v>3.37404116329859</v>
@@ -4293,10 +4293,10 @@
         <v>2014-10</v>
       </c>
       <c r="B281">
-        <v>103.833577752903</v>
+        <v>103.738304019854</v>
       </c>
       <c r="C281">
-        <v>102.700844175259</v>
+        <v>103.4195448692</v>
       </c>
       <c r="D281">
         <v>3.2866083611506</v>
@@ -4307,10 +4307,10 @@
         <v>2014-11</v>
       </c>
       <c r="B282">
-        <v>103.671523017708</v>
+        <v>103.731062876693</v>
       </c>
       <c r="C282">
-        <v>102.277611046127</v>
+        <v>102.611426598287</v>
       </c>
       <c r="D282">
         <v>3.27059016394628</v>
@@ -4321,10 +4321,10 @@
         <v>2014-12</v>
       </c>
       <c r="B283">
-        <v>102.463325001548</v>
+        <v>103.298930425265</v>
       </c>
       <c r="C283">
-        <v>100.545993197178</v>
+        <v>100.815319370416</v>
       </c>
       <c r="D283">
         <v>3.32540676054684</v>
@@ -4335,10 +4335,10 @@
         <v>2015-01</v>
       </c>
       <c r="B284">
-        <v>99.977776080033</v>
+        <v>99.7737033761291</v>
       </c>
       <c r="C284">
-        <v>97.2674605130619</v>
+        <v>97.6233508771877</v>
       </c>
       <c r="D284">
         <v>3.45058765274322</v>
@@ -4349,10 +4349,10 @@
         <v>2015-02</v>
       </c>
       <c r="B285">
-        <v>98.5518701707253</v>
+        <v>98.4145165069251</v>
       </c>
       <c r="C285">
-        <v>96.4715360601951</v>
+        <v>97.3723898762138</v>
       </c>
       <c r="D285">
         <v>3.52015114204384</v>
@@ -4363,10 +4363,10 @@
         <v>2015-03</v>
       </c>
       <c r="B286">
-        <v>99.0910717564145</v>
+        <v>98.9899006007393</v>
       </c>
       <c r="C286">
-        <v>96.0775600109647</v>
+        <v>95.9402571744183</v>
       </c>
       <c r="D286">
         <v>3.53444413687814</v>
@@ -4377,10 +4377,10 @@
         <v>2015-04</v>
       </c>
       <c r="B287">
-        <v>99.6285561269899</v>
+        <v>98.7850191175607</v>
       </c>
       <c r="C287">
-        <v>97.7632841026297</v>
+        <v>97.6105928879995</v>
       </c>
       <c r="D287">
         <v>3.49390076036937</v>
@@ -4391,10 +4391,10 @@
         <v>2015-05</v>
       </c>
       <c r="B288">
-        <v>100.482123745785</v>
+        <v>100.456931983685</v>
       </c>
       <c r="C288">
-        <v>97.790991729318</v>
+        <v>97.8761554688356</v>
       </c>
       <c r="D288">
         <v>3.4466226382184</v>
@@ -4405,10 +4405,10 @@
         <v>2015-06</v>
       </c>
       <c r="B289">
-        <v>99.4741510612231</v>
+        <v>99.9521250681335</v>
       </c>
       <c r="C289">
-        <v>97.1532667848296</v>
+        <v>97.1446200065313</v>
       </c>
       <c r="D289">
         <v>3.39268886596659</v>
@@ -4419,10 +4419,10 @@
         <v>2015-07</v>
       </c>
       <c r="B290">
-        <v>99.4280939918852</v>
+        <v>99.2421820863972</v>
       </c>
       <c r="C290">
-        <v>95.8980170509854</v>
+        <v>95.6732056220906</v>
       </c>
       <c r="D290">
         <v>3.33218237097368</v>
@@ -4433,10 +4433,10 @@
         <v>2015-08</v>
       </c>
       <c r="B291">
-        <v>99.6948250664737</v>
+        <v>99.8567222597706</v>
       </c>
       <c r="C291">
-        <v>95.5566432992007</v>
+        <v>96.3370831626315</v>
       </c>
       <c r="D291">
         <v>3.27636457935363</v>
@@ -4447,10 +4447,10 @@
         <v>2015-09</v>
       </c>
       <c r="B292">
-        <v>98.4863927430818</v>
+        <v>97.9403994731301</v>
       </c>
       <c r="C292">
-        <v>93.9794469606491</v>
+        <v>93.5609430388178</v>
       </c>
       <c r="D292">
         <v>3.22512760096565</v>
@@ -4461,10 +4461,10 @@
         <v>2015-10</v>
       </c>
       <c r="B293">
-        <v>96.7523312205991</v>
+        <v>96.547892944679</v>
       </c>
       <c r="C293">
-        <v>91.8002848334739</v>
+        <v>91.532336866726</v>
       </c>
       <c r="D293">
         <v>3.17837574335759</v>
@@ -4475,10 +4475,10 @@
         <v>2015-11</v>
       </c>
       <c r="B294">
-        <v>97.9065773537371</v>
+        <v>97.7710872448346</v>
       </c>
       <c r="C294">
-        <v>93.1679416537732</v>
+        <v>92.8926965687741</v>
       </c>
       <c r="D294">
         <v>3.13541025880542</v>
@@ -4489,10 +4489,10 @@
         <v>2015-12</v>
       </c>
       <c r="B295">
-        <v>97.5595540035365</v>
+        <v>97.2438400614346</v>
       </c>
       <c r="C295">
-        <v>93.8206328823492</v>
+        <v>94.2844401716138</v>
       </c>
       <c r="D295">
         <v>3.09625963135642</v>
@@ -4503,10 +4503,10 @@
         <v>2016-01</v>
       </c>
       <c r="B296">
-        <v>97.7699993783535</v>
+        <v>97.4704781817886</v>
       </c>
       <c r="C296">
-        <v>96.8390895669199</v>
+        <v>96.8393659364909</v>
       </c>
       <c r="D296">
         <v>3.06094197780389</v>
@@ -4517,10 +4517,10 @@
         <v>2016-02</v>
       </c>
       <c r="B297">
-        <v>95.1180183323911</v>
+        <v>94.897750395004</v>
       </c>
       <c r="C297">
-        <v>95.8850489006801</v>
+        <v>96.2544333365103</v>
       </c>
       <c r="D297">
         <v>3.03351237574343</v>
@@ -4531,10 +4531,10 @@
         <v>2016-03</v>
       </c>
       <c r="B298">
-        <v>93.4248234934441</v>
+        <v>92.97232094691</v>
       </c>
       <c r="C298">
-        <v>94.2374241090401</v>
+        <v>94.4506726154108</v>
       </c>
       <c r="D298">
         <v>3.01387662786389</v>
@@ -4545,10 +4545,10 @@
         <v>2016-04</v>
       </c>
       <c r="B299">
-        <v>94.5526280951796</v>
+        <v>94.9092574355028</v>
       </c>
       <c r="C299">
-        <v>96.1670937976948</v>
+        <v>96.769267324611</v>
       </c>
       <c r="D299">
         <v>3.00195358846034</v>
@@ -4559,10 +4559,10 @@
         <v>2016-05</v>
       </c>
       <c r="B300">
-        <v>95.7844691607223</v>
+        <v>95.7564995045682</v>
       </c>
       <c r="C300">
-        <v>100.092377905266</v>
+        <v>100.385260528798</v>
       </c>
       <c r="D300">
         <v>2.99909320315983</v>
@@ -4573,10 +4573,10 @@
         <v>2016-06</v>
       </c>
       <c r="B301">
-        <v>96.3952495250088</v>
+        <v>95.6763350225962</v>
       </c>
       <c r="C301">
-        <v>100.343169582444</v>
+        <v>100.460468075239</v>
       </c>
       <c r="D301">
         <v>3.00522491049816</v>
@@ -4587,10 +4587,10 @@
         <v>2016-07</v>
       </c>
       <c r="B302">
-        <v>96.6794463517495</v>
+        <v>96.8949930643605</v>
       </c>
       <c r="C302">
-        <v>101.167626715006</v>
+        <v>101.706747852286</v>
       </c>
       <c r="D302">
         <v>3.02027599353806</v>
@@ -4601,10 +4601,10 @@
         <v>2016-08</v>
       </c>
       <c r="B303">
-        <v>98.0150005528149</v>
+        <v>97.5035406596246</v>
       </c>
       <c r="C303">
-        <v>101.859173875813</v>
+        <v>102.284952034322</v>
       </c>
       <c r="D303">
         <v>3.07528157129499</v>
@@ -4615,10 +4615,10 @@
         <v>2016-09</v>
       </c>
       <c r="B304">
-        <v>98.8481311383076</v>
+        <v>99.2759031182912</v>
       </c>
       <c r="C304">
-        <v>105.103449179372</v>
+        <v>105.284215983919</v>
       </c>
       <c r="D304">
         <v>3.17002086243544</v>
@@ -4629,10 +4629,10 @@
         <v>2016-10</v>
       </c>
       <c r="B305">
-        <v>100.005714196233</v>
+        <v>99.4941752633273</v>
       </c>
       <c r="C305">
-        <v>107.759677192161</v>
+        <v>107.973442698905</v>
       </c>
       <c r="D305">
         <v>3.30436101689784</v>
@@ -4643,10 +4643,10 @@
         <v>2016-11</v>
       </c>
       <c r="B306">
-        <v>101.236417978516</v>
+        <v>101.0701267664</v>
       </c>
       <c r="C306">
-        <v>108.364457178652</v>
+        <v>108.816629077467</v>
       </c>
       <c r="D306">
         <v>3.3829305592501</v>
@@ -4657,10 +4657,10 @@
         <v>2016-12</v>
       </c>
       <c r="B307">
-        <v>103.507868676979</v>
+        <v>103.255058089815</v>
       </c>
       <c r="C307">
-        <v>109.258763257818</v>
+        <v>109.757001332325</v>
       </c>
       <c r="D307">
         <v>3.40596573951599</v>
@@ -4671,10 +4671,10 @@
         <v>2017-01</v>
       </c>
       <c r="B308">
-        <v>105.280716694475</v>
+        <v>105.642189372069</v>
       </c>
       <c r="C308">
-        <v>110.915348901646</v>
+        <v>110.814990864665</v>
       </c>
       <c r="D308">
         <v>3.37385869742428</v>
@@ -4685,10 +4685,10 @@
         <v>2017-02</v>
       </c>
       <c r="B309">
-        <v>108.771609465143</v>
+        <v>108.804850291141</v>
       </c>
       <c r="C309">
-        <v>113.537603328931</v>
+        <v>113.158887746689</v>
       </c>
       <c r="D309">
         <v>3.39539183857364</v>
@@ -4699,10 +4699,10 @@
         <v>2017-03</v>
       </c>
       <c r="B310">
-        <v>110.17910087065</v>
+        <v>110.65782118057</v>
       </c>
       <c r="C310">
-        <v>114.175403347065</v>
+        <v>114.505937750458</v>
       </c>
       <c r="D310">
         <v>3.47012207951363</v>
@@ -4713,10 +4713,10 @@
         <v>2017-04</v>
       </c>
       <c r="B311">
-        <v>111.399185764476</v>
+        <v>111.023371964211</v>
       </c>
       <c r="C311">
-        <v>114.501671729289</v>
+        <v>114.473334620611</v>
       </c>
       <c r="D311">
         <v>3.59766909536982</v>
@@ -4727,10 +4727,10 @@
         <v>2017-05</v>
       </c>
       <c r="B312">
-        <v>111.310749992918</v>
+        <v>111.193951254699</v>
       </c>
       <c r="C312">
-        <v>111.906358157068</v>
+        <v>112.173344499631</v>
       </c>
       <c r="D312">
         <v>3.712549121048</v>
@@ -4741,10 +4741,10 @@
         <v>2017-06</v>
       </c>
       <c r="B313">
-        <v>112.699922608324</v>
+        <v>112.007848548494</v>
       </c>
       <c r="C313">
-        <v>113.670528784016</v>
+        <v>114.101182735354</v>
       </c>
       <c r="D313">
         <v>3.81481177245524</v>
@@ -4755,10 +4755,10 @@
         <v>2017-07</v>
       </c>
       <c r="B314">
-        <v>113.962770182624</v>
+        <v>113.316052572865</v>
       </c>
       <c r="C314">
-        <v>113.928538020607</v>
+        <v>114.508885981156</v>
       </c>
       <c r="D314">
         <v>3.90451678495671</v>
@@ -4769,10 +4769,10 @@
         <v>2017-08</v>
       </c>
       <c r="B315">
-        <v>113.696751930279</v>
+        <v>113.420315470389</v>
       </c>
       <c r="C315">
-        <v>111.898894906152</v>
+        <v>112.849354500647</v>
       </c>
       <c r="D315">
         <v>3.96633450727887</v>
@@ -4783,10 +4783,10 @@
         <v>2017-09</v>
       </c>
       <c r="B316">
-        <v>113.810200926645</v>
+        <v>113.359536908811</v>
       </c>
       <c r="C316">
-        <v>111.553164622809</v>
+        <v>112.582698062008</v>
       </c>
       <c r="D316">
         <v>4.00050001873844</v>
@@ -4797,10 +4797,10 @@
         <v>2017-10</v>
       </c>
       <c r="B317">
-        <v>116.140022401789</v>
+        <v>116.257507912691</v>
       </c>
       <c r="C317">
-        <v>112.294557258589</v>
+        <v>112.945879497609</v>
       </c>
       <c r="D317">
         <v>4.00725005245116</v>
@@ -4811,10 +4811,10 @@
         <v>2017-11</v>
       </c>
       <c r="B318">
-        <v>115.885803610222</v>
+        <v>115.671711275643</v>
       </c>
       <c r="C318">
-        <v>111.348167862214</v>
+        <v>112.136214327006</v>
       </c>
       <c r="D318">
         <v>4.03998236367471</v>
@@ -4825,10 +4825,10 @@
         <v>2017-12</v>
       </c>
       <c r="B319">
-        <v>117.187809995227</v>
+        <v>116.78410373599</v>
       </c>
       <c r="C319">
-        <v>109.900465978298</v>
+        <v>110.116811027432</v>
       </c>
       <c r="D319">
         <v>4.09848139527267</v>
@@ -4839,10 +4839,10 @@
         <v>2018-01</v>
       </c>
       <c r="B320">
-        <v>116.998800772829</v>
+        <v>116.856858419041</v>
       </c>
       <c r="C320">
-        <v>107.279750854994</v>
+        <v>108.422373060881</v>
       </c>
       <c r="D320">
         <v>4.18254291499942</v>
@@ -4853,10 +4853,10 @@
         <v>2018-02</v>
       </c>
       <c r="B321">
-        <v>116.582395429402</v>
+        <v>116.447532973802</v>
       </c>
       <c r="C321">
-        <v>106.76235137206</v>
+        <v>107.694411805323</v>
       </c>
       <c r="D321">
         <v>4.2177122616842</v>
@@ -4867,10 +4867,10 @@
         <v>2018-03</v>
       </c>
       <c r="B322">
-        <v>115.61297388417</v>
+        <v>115.962763200483</v>
       </c>
       <c r="C322">
-        <v>104.836746988319</v>
+        <v>105.475872483542</v>
       </c>
       <c r="D322">
         <v>4.20439888369295</v>
@@ -4881,10 +4881,10 @@
         <v>2018-04</v>
       </c>
       <c r="B323">
-        <v>114.026386959656</v>
+        <v>114.276133651513</v>
       </c>
       <c r="C323">
-        <v>103.708687602385</v>
+        <v>104.131150108386</v>
       </c>
       <c r="D323">
         <v>4.14310366220312</v>
@@ -4895,10 +4895,10 @@
         <v>2018-05</v>
       </c>
       <c r="B324">
-        <v>113.266577762753</v>
+        <v>113.11600879325</v>
       </c>
       <c r="C324">
-        <v>101.391673302979</v>
+        <v>102.49400862834</v>
       </c>
       <c r="D324">
         <v>4.05025193355621</v>
@@ -4909,10 +4909,10 @@
         <v>2018-06</v>
       </c>
       <c r="B325">
-        <v>112.560632012324</v>
+        <v>113.346583907887</v>
       </c>
       <c r="C325">
-        <v>102.076818924639</v>
+        <v>102.657578866987</v>
       </c>
       <c r="D325">
         <v>3.92619936150706</v>
@@ -4923,10 +4923,10 @@
         <v>2018-07</v>
       </c>
       <c r="B326">
-        <v>111.067900171</v>
+        <v>110.990104669305</v>
       </c>
       <c r="C326">
-        <v>100.677944426272</v>
+        <v>101.216932409176</v>
       </c>
       <c r="D326">
         <v>3.77130107490682</v>
@@ -4937,10 +4937,10 @@
         <v>2018-08</v>
       </c>
       <c r="B327">
-        <v>107.904314518146</v>
+        <v>108.209689705751</v>
       </c>
       <c r="C327">
-        <v>99.5836013100832</v>
+        <v>99.9402244997217</v>
       </c>
       <c r="D327">
         <v>3.61243354644407</v>
@@ -4951,10 +4951,10 @@
         <v>2018-09</v>
       </c>
       <c r="B328">
-        <v>107.87801908156</v>
+        <v>107.619091669411</v>
       </c>
       <c r="C328">
-        <v>97.1973831744036</v>
+        <v>97.1272867069762</v>
       </c>
       <c r="D328">
         <v>3.44952541064578</v>
@@ -4965,10 +4965,10 @@
         <v>2018-10</v>
       </c>
       <c r="B329">
-        <v>105.573665284462</v>
+        <v>105.885490511924</v>
       </c>
       <c r="C329">
-        <v>94.5057770955049</v>
+        <v>94.4726606328141</v>
       </c>
       <c r="D329">
         <v>3.28250054481676</v>
@@ -4979,10 +4979,10 @@
         <v>2018-11</v>
       </c>
       <c r="B330">
-        <v>101.964233945207</v>
+        <v>102.538896438812</v>
       </c>
       <c r="C330">
-        <v>94.0621455710273</v>
+        <v>93.8673164736186</v>
       </c>
       <c r="D330">
         <v>3.15721944001453</v>
@@ -4993,10 +4993,10 @@
         <v>2018-12</v>
       </c>
       <c r="B331">
-        <v>99.6621998388245</v>
+        <v>100.008503319046</v>
       </c>
       <c r="C331">
-        <v>92.9657691067596</v>
+        <v>93.4620701180719</v>
       </c>
       <c r="D331">
         <v>3.07335969247804</v>
@@ -5007,10 +5007,10 @@
         <v>2019-01</v>
       </c>
       <c r="B332">
-        <v>98.251437836168</v>
+        <v>98.0164101107115</v>
       </c>
       <c r="C332">
-        <v>92.7163089139691</v>
+        <v>92.8668702130523</v>
       </c>
       <c r="D332">
         <v>3.03055563366637</v>
@@ -5021,10 +5021,10 @@
         <v>2019-02</v>
       </c>
       <c r="B333">
-        <v>94.5973793130373</v>
+        <v>94.2913269737669</v>
       </c>
       <c r="C333">
-        <v>89.8792681926053</v>
+        <v>89.6266180280151</v>
       </c>
       <c r="D333">
         <v>3.01697720740772</v>
@@ -5035,10 +5035,10 @@
         <v>2019-03</v>
       </c>
       <c r="B334">
-        <v>95.9864373775804</v>
+        <v>94.888537903802</v>
       </c>
       <c r="C334">
-        <v>91.8189164718345</v>
+        <v>91.7120661203462</v>
       </c>
       <c r="D334">
         <v>3.03232391651029</v>
@@ -5049,10 +5049,10 @@
         <v>2019-04</v>
       </c>
       <c r="B335">
-        <v>97.7309437857006</v>
+        <v>97.4752682187684</v>
       </c>
       <c r="C335">
-        <v>93.9703500034565</v>
+        <v>93.6292740368208</v>
       </c>
       <c r="D335">
         <v>3.07632164018938</v>
@@ -5063,10 +5063,10 @@
         <v>2019-05</v>
       </c>
       <c r="B336">
-        <v>96.3621822375212</v>
+        <v>96.5793635836958</v>
       </c>
       <c r="C336">
-        <v>95.3616761404354</v>
+        <v>94.4728021924417</v>
       </c>
       <c r="D336">
         <v>3.1170220969712</v>
@@ -5077,10 +5077,10 @@
         <v>2019-06</v>
       </c>
       <c r="B337">
-        <v>96.3228776576118</v>
+        <v>95.4300828253835</v>
       </c>
       <c r="C337">
-        <v>92.6453023428834</v>
+        <v>91.7860767637571</v>
       </c>
       <c r="D337">
         <v>3.15448736781806</v>
@@ -5091,10 +5091,10 @@
         <v>2019-07</v>
       </c>
       <c r="B338">
-        <v>94.677485013035</v>
+        <v>94.5433180542753</v>
       </c>
       <c r="C338">
-        <v>91.2466157233508</v>
+        <v>90.8705337325106</v>
       </c>
       <c r="D338">
         <v>3.18877342117798</v>
@@ -5105,10 +5105,10 @@
         <v>2019-08</v>
       </c>
       <c r="B339">
-        <v>93.5822010641966</v>
+        <v>93.3433396078702</v>
       </c>
       <c r="C339">
-        <v>90.6642417070059</v>
+        <v>90.0559893902605</v>
       </c>
       <c r="D339">
         <v>3.18103712074785</v>
@@ -5119,10 +5119,10 @@
         <v>2019-09</v>
       </c>
       <c r="B340">
-        <v>92.3059600969353</v>
+        <v>91.524501714199</v>
       </c>
       <c r="C340">
-        <v>89.9721067411185</v>
+        <v>90.1068384033921</v>
       </c>
       <c r="D340">
         <v>3.13151618453522</v>
@@ -5133,10 +5133,10 @@
         <v>2019-10</v>
       </c>
       <c r="B341">
-        <v>91.8483474756058</v>
+        <v>91.1524499426636</v>
       </c>
       <c r="C341">
-        <v>90.6924272044709</v>
+        <v>90.4093245708249</v>
       </c>
       <c r="D341">
         <v>3.04037506347325</v>
@@ -5147,10 +5147,10 @@
         <v>2019-11</v>
       </c>
       <c r="B342">
-        <v>91.7789199625433</v>
+        <v>90.7601283540861</v>
       </c>
       <c r="C342">
-        <v>89.9903361846702</v>
+        <v>89.4962437819991</v>
       </c>
       <c r="D342">
         <v>2.87253187925647</v>
@@ -5161,10 +5161,10 @@
         <v>2019-12</v>
       </c>
       <c r="B343">
-        <v>93.546961696196</v>
+        <v>92.6499130778676</v>
       </c>
       <c r="C343">
-        <v>94.3412804101991</v>
+        <v>94.0412245351723</v>
       </c>
       <c r="D343">
         <v>2.62872892922657</v>
@@ -5175,10 +5175,10 @@
         <v>2020-01</v>
       </c>
       <c r="B344">
-        <v>94.6014597255024</v>
+        <v>94.344701984932</v>
       </c>
       <c r="C344">
-        <v>96.2524882281204</v>
+        <v>96.1323977083575</v>
       </c>
     </row>
     <row r="345">
@@ -5186,10 +5186,10 @@
         <v>2020-02</v>
       </c>
       <c r="B345">
-        <v>96.8069056101342</v>
+        <v>96.2506677890546</v>
       </c>
       <c r="C345">
-        <v>98.0437827940165</v>
+        <v>97.6329732547201</v>
       </c>
     </row>
     <row r="346">
@@ -5197,10 +5197,10 @@
         <v>2020-03</v>
       </c>
       <c r="B346">
-        <v>84.2240763019999</v>
+        <v>81.3639063998154</v>
       </c>
       <c r="C346">
-        <v>86.4834046673767</v>
+        <v>86.7200732031403</v>
       </c>
     </row>
     <row r="347">
@@ -5208,10 +5208,10 @@
         <v>2020-04</v>
       </c>
       <c r="B347">
-        <v>80.4381775984085</v>
+        <v>80.4442978088975</v>
       </c>
       <c r="C347">
-        <v>79.1510341336823</v>
+        <v>78.8306258621386</v>
       </c>
     </row>
     <row r="348">
@@ -5219,10 +5219,10 @@
         <v>2020-05</v>
       </c>
       <c r="B348">
-        <v>57.4518843785034</v>
+        <v>55.2300050323631</v>
       </c>
       <c r="C348">
-        <v>50.7360795218959</v>
+        <v>49.1275761995569</v>
       </c>
     </row>
     <row r="349">
@@ -5230,10 +5230,10 @@
         <v>2020-06</v>
       </c>
       <c r="B349">
-        <v>62.4450605395139</v>
+        <v>60.7760030503221</v>
       </c>
       <c r="C349">
-        <v>56.3645184839234</v>
+        <v>56.5368139866403</v>
       </c>
     </row>
     <row r="350">
@@ -5241,10 +5241,10 @@
         <v>2020-07</v>
       </c>
       <c r="B350">
-        <v>71.6220878863743</v>
+        <v>72.1744160987531</v>
       </c>
       <c r="C350">
-        <v>74.8053488186876</v>
+        <v>76.2799636104605</v>
       </c>
     </row>
     <row r="351">
@@ -5252,10 +5252,10 @@
         <v>2020-08</v>
       </c>
       <c r="B351">
-        <v>84.7875265375667</v>
+        <v>86.1911958325573</v>
       </c>
       <c r="C351">
-        <v>101.826201165053</v>
+        <v>101.909172583022</v>
       </c>
     </row>
     <row r="352">
@@ -5263,10 +5263,10 @@
         <v>2020-09</v>
       </c>
       <c r="B352">
-        <v>92.1151097018327</v>
+        <v>91.7781971409618</v>
       </c>
       <c r="C352">
-        <v>108.008008559818</v>
+        <v>105.881541743031</v>
       </c>
     </row>
     <row r="353">
@@ -5274,10 +5274,10 @@
         <v>2020-10</v>
       </c>
       <c r="B353">
-        <v>96.1856270826358</v>
+        <v>95.7955126793027</v>
       </c>
       <c r="C353">
-        <v>110.606178141404</v>
+        <v>109.117884587782</v>
       </c>
     </row>
     <row r="354">
@@ -5285,10 +5285,10 @@
         <v>2020-11</v>
       </c>
       <c r="B354">
-        <v>101.965083796807</v>
+        <v>103.05803160216</v>
       </c>
       <c r="C354">
-        <v>110.59256680746</v>
+        <v>109.465810118943</v>
       </c>
     </row>
     <row r="355">
@@ -5296,10 +5296,10 @@
         <v>2020-12</v>
       </c>
       <c r="B355">
-        <v>100.998642864133</v>
+        <v>102.673909848609</v>
       </c>
       <c r="C355">
-        <v>107.732806224329</v>
+        <v>107.198745713</v>
       </c>
     </row>
     <row r="356">
@@ -5307,10 +5307,10 @@
         <v>2021-01</v>
       </c>
       <c r="B356">
-        <v>101.589002116285</v>
+        <v>102.400781176276</v>
       </c>
       <c r="C356">
-        <v>109.767495407062</v>
+        <v>108.88271470863</v>
       </c>
     </row>
     <row r="357">
@@ -5318,10 +5318,10 @@
         <v>2021-02</v>
       </c>
       <c r="B357">
-        <v>103.130492176723</v>
+        <v>103.930067850572</v>
       </c>
       <c r="C357">
-        <v>107.493305058599</v>
+        <v>107.906199560035</v>
       </c>
     </row>
     <row r="358">
@@ -5329,10 +5329,10 @@
         <v>2021-03</v>
       </c>
       <c r="B358">
-        <v>106.640477478563</v>
+        <v>107.479869623971</v>
       </c>
       <c r="C358">
-        <v>112.910743594297</v>
+        <v>107.768584322602</v>
       </c>
     </row>
     <row r="359">
@@ -5340,10 +5340,10 @@
         <v>2021-04</v>
       </c>
       <c r="B359">
-        <v>112.857725640218</v>
+        <v>112.793570865736</v>
       </c>
       <c r="C359">
-        <v>118.805394394185</v>
+        <v>118.604602578669</v>
       </c>
     </row>
     <row r="360">
@@ -5351,10 +5351,10 @@
         <v>2021-05</v>
       </c>
       <c r="B360">
-        <v>126.711213306631</v>
+        <v>126.975815721737</v>
       </c>
       <c r="C360">
-        <v>131.480921319612</v>
+        <v>133.411625413771</v>
       </c>
     </row>
     <row r="361">
@@ -5362,10 +5362,10 @@
         <v>2021-06</v>
       </c>
       <c r="B361">
-        <v>127.040928728033</v>
+        <v>127.733137831598</v>
       </c>
       <c r="C361">
-        <v>129.304608022936</v>
+        <v>129.131999758244</v>
       </c>
     </row>
     <row r="362">
@@ -5373,10 +5373,10 @@
         <v>2021-07</v>
       </c>
       <c r="B362">
-        <v>126.214784225553</v>
+        <v>125.796479900028</v>
       </c>
       <c r="C362">
-        <v>123.958640534163</v>
+        <v>123.408715621258</v>
       </c>
     </row>
     <row r="363">
@@ -5384,10 +5384,10 @@
         <v>2021-08</v>
       </c>
       <c r="B363">
-        <v>122.679522171159</v>
+        <v>121.53268663643</v>
       </c>
       <c r="C363">
-        <v>118.325412937344</v>
+        <v>117.580278779636</v>
       </c>
     </row>
     <row r="364">
@@ -5395,10 +5395,10 @@
         <v>2021-09</v>
       </c>
       <c r="B364">
-        <v>115.671118744041</v>
+        <v>115.781378017785</v>
       </c>
       <c r="C364">
-        <v>112.464957161343</v>
+        <v>113.066041209697</v>
       </c>
     </row>
     <row r="365">
@@ -5406,10 +5406,10 @@
         <v>2021-10</v>
       </c>
       <c r="B365">
-        <v>113.495207302354</v>
+        <v>112.21687238318</v>
       </c>
       <c r="C365">
-        <v>107.305568855599</v>
+        <v>107.020233679217</v>
       </c>
     </row>
     <row r="366">
@@ -5417,10 +5417,10 @@
         <v>2021-11</v>
       </c>
       <c r="B366">
-        <v>110.637474827666</v>
+        <v>109.539962078507</v>
       </c>
       <c r="C366">
-        <v>105.925126307418</v>
+        <v>105.497495070366</v>
       </c>
     </row>
     <row r="367">
@@ -5428,10 +5428,10 @@
         <v>2021-12</v>
       </c>
       <c r="B367">
-        <v>112.996461543191</v>
+        <v>112.267007417777</v>
       </c>
       <c r="C367">
-        <v>108.162587087308</v>
+        <v>107.857298773432</v>
       </c>
     </row>
     <row r="368">
@@ -5439,10 +5439,10 @@
         <v>2022-01</v>
       </c>
       <c r="B368">
-        <v>111.187583375298</v>
+        <v>111.367640129206</v>
       </c>
       <c r="C368">
-        <v>106.631137332787</v>
+        <v>105.900916894212</v>
       </c>
     </row>
     <row r="369">
@@ -5450,10 +5450,10 @@
         <v>2022-02</v>
       </c>
       <c r="B369">
-        <v>110.332896272113</v>
+        <v>109.968545330681</v>
       </c>
       <c r="C369">
-        <v>105.944481068545</v>
+        <v>105.18922526273</v>
       </c>
     </row>
     <row r="370">
@@ -5461,10 +5461,10 @@
         <v>2022-03</v>
       </c>
       <c r="B370">
-        <v>107.695862336693</v>
+        <v>107.282177367609</v>
       </c>
       <c r="C370">
-        <v>103.133834278948</v>
+        <v>101.782424746299</v>
       </c>
     </row>
     <row r="371">
@@ -5472,10 +5472,10 @@
         <v>2022-04</v>
       </c>
       <c r="B371">
-        <v>102.073227842028</v>
+        <v>102.242095804296</v>
       </c>
       <c r="C371">
-        <v>99.2216699442087</v>
+        <v>98.2119023049007</v>
       </c>
     </row>
     <row r="372">
@@ -5483,10 +5483,10 @@
         <v>2022-05</v>
       </c>
       <c r="B372">
-        <v>99.1100372890879</v>
+        <v>98.5569201272392</v>
       </c>
       <c r="C372">
-        <v>95.506828605969</v>
+        <v>95.013927048045</v>
       </c>
     </row>
     <row r="373">
@@ -5494,10 +5494,10 @@
         <v>2022-06</v>
       </c>
       <c r="B373">
-        <v>97.0799671902177</v>
+        <v>98.7807332673097</v>
       </c>
       <c r="C373">
-        <v>95.9328099868458</v>
+        <v>97.1862902870331</v>
       </c>
     </row>
     <row r="374">
@@ -5505,10 +5505,10 @@
         <v>2022-07</v>
       </c>
       <c r="B374">
-        <v>95.8347897098829</v>
+        <v>96.418363916026</v>
       </c>
       <c r="C374">
-        <v>92.9229758448579</v>
+        <v>92.5640805478533</v>
       </c>
     </row>
     <row r="375">
@@ -5516,10 +5516,10 @@
         <v>2022-08</v>
       </c>
       <c r="B375">
-        <v>92.1469888359813</v>
+        <v>92.2690515898457</v>
       </c>
       <c r="C375">
-        <v>87.7372050805534</v>
+        <v>88.410462263988</v>
       </c>
     </row>
     <row r="376">
@@ -5527,10 +5527,10 @@
         <v>2022-09</v>
       </c>
       <c r="B376">
-        <v>93.8490092106238</v>
+        <v>94.4621993903801</v>
       </c>
       <c r="C376">
-        <v>90.8473003526273</v>
+        <v>89.8832501870404</v>
       </c>
     </row>
     <row r="377">
@@ -5538,10 +5538,10 @@
         <v>2022-10</v>
       </c>
       <c r="B377">
-        <v>90.9364315871489</v>
+        <v>92.2456521423671</v>
       </c>
       <c r="C377">
-        <v>90.5954256988864</v>
+        <v>91.3651870214107</v>
       </c>
     </row>
     <row r="378">
@@ -5549,10 +5549,10 @@
         <v>2022-11</v>
       </c>
       <c r="B378">
-        <v>89.0202202933199</v>
+        <v>90.7190744209385</v>
       </c>
       <c r="C378">
-        <v>91.7270906317269</v>
+        <v>91.574145673996</v>
       </c>
     </row>
     <row r="379">
@@ -5560,10 +5560,10 @@
         <v>2022-12</v>
       </c>
       <c r="B379">
-        <v>86.8903716488031</v>
+        <v>87.5649397321722</v>
       </c>
       <c r="C379">
-        <v>88.8960129255351</v>
+        <v>88.8199274652982</v>
       </c>
     </row>
     <row r="380">
@@ -5571,10 +5571,10 @@
         <v>2023-01</v>
       </c>
       <c r="B380">
-        <v>85.6941770900679</v>
+        <v>86.7992611398764</v>
       </c>
       <c r="C380">
-        <v>89.191682332391</v>
+        <v>88.112210842828</v>
       </c>
     </row>
     <row r="381">
@@ -5582,10 +5582,10 @@
         <v>2023-02</v>
       </c>
       <c r="B381">
-        <v>89.0341650253954</v>
+        <v>89.4124565983561</v>
       </c>
       <c r="C381">
-        <v>90.161654742469</v>
+        <v>89.4709388350466</v>
       </c>
     </row>
     <row r="382">
@@ -5593,10 +5593,10 @@
         <v>2023-03</v>
       </c>
       <c r="B382">
-        <v>92.5375348839797</v>
+        <v>93.8427211934342</v>
       </c>
       <c r="C382">
-        <v>93.5930891387901</v>
+        <v>93.5135248145072</v>
       </c>
     </row>
     <row r="383">
@@ -5604,13 +5604,13 @@
         <v>2023-04</v>
       </c>
       <c r="B383">
-        <v>92.4820153581307</v>
+        <v>93.4001652482908</v>
       </c>
       <c r="C383">
-        <v>93.1456297413878</v>
+        <v>92.3767932396921</v>
       </c>
       <c r="D383">
-        <v>3.73226603851191</v>
+        <v>3.73226617019127</v>
       </c>
     </row>
     <row r="384">
@@ -5618,13 +5618,13 @@
         <v>2023-05</v>
       </c>
       <c r="B384">
-        <v>94.2481804849551</v>
+        <v>94.8283485607562</v>
       </c>
       <c r="C384">
-        <v>95.3837553662648</v>
+        <v>94.5297404586073</v>
       </c>
       <c r="D384">
-        <v>3.86126107141207</v>
+        <v>3.86126112687444</v>
       </c>
     </row>
     <row r="385">
@@ -5632,13 +5632,13 @@
         <v>2023-06</v>
       </c>
       <c r="B385">
-        <v>94.1050153406754</v>
+        <v>93.6375440241243</v>
       </c>
       <c r="C385">
-        <v>94.8167727835092</v>
+        <v>93.9610659801532</v>
       </c>
       <c r="D385">
-        <v>3.77221067648522</v>
+        <v>3.77221049041528</v>
       </c>
     </row>
     <row r="386">
@@ -5646,13 +5646,13 @@
         <v>2023-07</v>
       </c>
       <c r="B386">
-        <v>94.5663315985101</v>
+        <v>94.3196423837399</v>
       </c>
       <c r="C386">
-        <v>96.1638029114055</v>
+        <v>95.5483125399111</v>
       </c>
       <c r="D386">
-        <v>3.46843052081492</v>
+        <v>3.46842993150527</v>
       </c>
     </row>
     <row r="387">
@@ -5660,13 +5660,13 @@
         <v>2023-08</v>
       </c>
       <c r="B387">
-        <v>95.3552856375004</v>
+        <v>95.5323713343568</v>
       </c>
       <c r="C387">
-        <v>93.360045853565</v>
+        <v>92.845213526244</v>
       </c>
       <c r="D387">
-        <v>3.30116027092701</v>
+        <v>3.30116002359051</v>
       </c>
     </row>
     <row r="388">
@@ -5674,13 +5674,13 @@
         <v>2023-09</v>
       </c>
       <c r="B388">
-        <v>94.7186182459813</v>
+        <v>94.2866361472879</v>
       </c>
       <c r="C388">
-        <v>93.9462944615863</v>
+        <v>93.1534150588097</v>
       </c>
       <c r="D388">
-        <v>3.267659254788</v>
+        <v>3.26766008673449</v>
       </c>
     </row>
     <row r="389">
@@ -5688,13 +5688,13 @@
         <v>2023-10</v>
       </c>
       <c r="B389">
-        <v>97.4712768569595</v>
+        <v>96.8458855076684</v>
       </c>
       <c r="C389">
-        <v>93.398594458021</v>
+        <v>92.5372314729208</v>
       </c>
       <c r="D389">
-        <v>3.36672714384632</v>
+        <v>3.36672979285891</v>
       </c>
     </row>
     <row r="390">
@@ -5702,13 +5702,13 @@
         <v>2023-11</v>
       </c>
       <c r="B390">
-        <v>96.8189865608713</v>
+        <v>96.1213980919314</v>
       </c>
       <c r="C390">
-        <v>94.1071916387944</v>
+        <v>92.9691965006447</v>
       </c>
       <c r="D390">
-        <v>3.41897719667634</v>
+        <v>3.41897831173054</v>
       </c>
     </row>
     <row r="391">
@@ -5716,13 +5716,13 @@
         <v>2023-12</v>
       </c>
       <c r="B391">
-        <v>97.0047197065768</v>
+        <v>95.7805135795634</v>
       </c>
       <c r="C391">
-        <v>95.6096332406171</v>
+        <v>93.5622606155139</v>
       </c>
       <c r="D391">
-        <v>3.42448768350148</v>
+        <v>3.42448393154801</v>
       </c>
     </row>
     <row r="392">
@@ -5730,13 +5730,13 @@
         <v>2024-01</v>
       </c>
       <c r="B392">
-        <v>98.0852255865518</v>
+        <v>97.3686746008206</v>
       </c>
       <c r="C392">
-        <v>96.1676509249087</v>
+        <v>94.3264403501495</v>
       </c>
       <c r="D392">
-        <v>3.38355483525343</v>
+        <v>3.38354291664918</v>
       </c>
     </row>
     <row r="393">
@@ -5744,13 +5744,13 @@
         <v>2024-02</v>
       </c>
       <c r="B393">
-        <v>96.6679033053174</v>
+        <v>96.9002069056917</v>
       </c>
       <c r="C393">
-        <v>96.8371348892596</v>
+        <v>95.802340419029</v>
       </c>
       <c r="D393">
-        <v>3.29522314880877</v>
+        <v>3.29521814029852</v>
       </c>
     </row>
     <row r="394">
@@ -5758,13 +5758,13 @@
         <v>2024-03</v>
       </c>
       <c r="B394">
-        <v>95.8610289481519</v>
+        <v>95.2540336261965</v>
       </c>
       <c r="C394">
-        <v>97.828011009218</v>
+        <v>96.6240726174008</v>
       </c>
       <c r="D394">
-        <v>3.15996816130458</v>
+        <v>3.15998499691068</v>
       </c>
     </row>
     <row r="395">
@@ -5772,13 +5772,13 @@
         <v>2024-04</v>
       </c>
       <c r="B395">
-        <v>97.8208993712299</v>
+        <v>97.5285861981676</v>
       </c>
       <c r="C395">
-        <v>98.2531534324845</v>
+        <v>97.2691137976714</v>
       </c>
       <c r="D395">
-        <v>2.97829658457121</v>
+        <v>2.97835004566251</v>
       </c>
     </row>
     <row r="396">
@@ -5786,13 +5786,13 @@
         <v>2024-05</v>
       </c>
       <c r="B396">
-        <v>97.7601507639212</v>
+        <v>96.7159548473302</v>
       </c>
       <c r="C396">
-        <v>99.6119716276989</v>
+        <v>97.0185518019317</v>
       </c>
       <c r="D396">
-        <v>2.87203439444039</v>
+        <v>2.87205685436409</v>
       </c>
     </row>
     <row r="397">
@@ -5800,13 +5800,13 @@
         <v>2024-06</v>
       </c>
       <c r="B397">
-        <v>97.8201745720405</v>
+        <v>97.1224487303688</v>
       </c>
       <c r="C397">
-        <v>99.2378930867211</v>
+        <v>97.3870518209788</v>
       </c>
       <c r="D397">
-        <v>2.84043105470195</v>
+        <v>2.8403555695816</v>
       </c>
     </row>
     <row r="398">
@@ -5814,13 +5814,13 @@
         <v>2024-07</v>
       </c>
       <c r="B398">
-        <v>96.6572614363951</v>
+        <v>96.3057420198974</v>
       </c>
       <c r="C398">
-        <v>99.198374398404</v>
+        <v>97.2473498397205</v>
       </c>
       <c r="D398">
-        <v>2.88273426960266</v>
+        <v>2.88249458049286</v>
       </c>
     </row>
     <row r="399">
@@ -5828,13 +5828,13 @@
         <v>2024-08</v>
       </c>
       <c r="B399">
-        <v>97.0286103616136</v>
+        <v>96.1205904227157</v>
       </c>
       <c r="C399">
-        <v>99.2041617856602</v>
+        <v>96.8815581840812</v>
       </c>
       <c r="D399">
-        <v>2.96439114409309</v>
+        <v>2.96429038940506</v>
       </c>
     </row>
     <row r="400">
@@ -5842,13 +5842,13 @@
         <v>2024-09</v>
       </c>
       <c r="B400">
-        <v>97.0426875124936</v>
+        <v>96.5352954117966</v>
       </c>
       <c r="C400">
-        <v>99.3656622447236</v>
+        <v>97.3352119385222</v>
       </c>
       <c r="D400">
-        <v>3.08521673454199</v>
+        <v>3.08555575911511</v>
       </c>
     </row>
     <row r="401">
@@ -5856,13 +5856,13 @@
         <v>2024-10</v>
       </c>
       <c r="B401">
-        <v>96.612997158482</v>
+        <v>96.1011811713433</v>
       </c>
       <c r="C401">
-        <v>99.4836651644063</v>
+        <v>97.8953695150348</v>
       </c>
       <c r="D401">
-        <v>3.24516627880418</v>
+        <v>3.24624471760673</v>
       </c>
     </row>
     <row r="402">
@@ -5870,13 +5870,13 @@
         <v>2024-11</v>
       </c>
       <c r="B402">
-        <v>99.2099843921253</v>
+        <v>98.5425184338548</v>
       </c>
       <c r="C402">
-        <v>102.392299925696</v>
+        <v>100.767531060234</v>
       </c>
       <c r="D402">
-        <v>3.34994486680225</v>
+        <v>3.35039858490501</v>
       </c>
     </row>
     <row r="403">
@@ -5884,13 +5884,13 @@
         <v>2024-12</v>
       </c>
       <c r="B403">
-        <v>99.5345228070122</v>
+        <v>99.056748233014</v>
       </c>
       <c r="C403">
-        <v>102.684401274069</v>
+        <v>101.421410635065</v>
       </c>
       <c r="D403">
-        <v>3.39976821638636</v>
+        <v>3.39824161751643</v>
       </c>
     </row>
     <row r="404">
@@ -5898,13 +5898,13 @@
         <v>2025-01</v>
       </c>
       <c r="B404">
-        <v>99.3045869256699</v>
+        <v>98.5423649455973</v>
       </c>
       <c r="C404">
-        <v>102.276808558788</v>
+        <v>100.968612507117</v>
       </c>
       <c r="D404">
-        <v>3.39495924685605</v>
+        <v>3.39010787996456</v>
       </c>
     </row>
     <row r="405">
@@ -5912,13 +5912,13 @@
         <v>2025-02</v>
       </c>
       <c r="B405">
-        <v>100.226692626535</v>
+        <v>99.5516069731967</v>
       </c>
       <c r="C405">
-        <v>102.148354712923</v>
+        <v>100.941190298757</v>
       </c>
       <c r="D405">
-        <v>3.42000186998241</v>
+        <v>3.41796146091338</v>
       </c>
     </row>
     <row r="406">
@@ -5926,13 +5926,13 @@
         <v>2025-03</v>
       </c>
       <c r="B406">
-        <v>100.493664652474</v>
+        <v>99.7866085865932</v>
       </c>
       <c r="C406">
-        <v>101.922013449445</v>
+        <v>101.184555991386</v>
       </c>
       <c r="D406">
-        <v>3.47471915089761</v>
+        <v>3.48158674247388</v>
       </c>
     </row>
     <row r="407">
@@ -5940,13 +5940,13 @@
         <v>2025-04</v>
       </c>
       <c r="B407">
-        <v>98.6632323169583</v>
+        <v>97.8780553028463</v>
       </c>
       <c r="C407">
-        <v>100.125600255804</v>
+        <v>99.436038089794</v>
       </c>
       <c r="D407">
-        <v>3.55899386986135</v>
+        <v>3.58084007943941</v>
       </c>
     </row>
     <row r="408">
@@ -5954,13 +5954,13 @@
         <v>2025-05</v>
       </c>
       <c r="B408">
-        <v>95.6363250187745</v>
+        <v>94.6395497584104</v>
       </c>
       <c r="C408">
-        <v>96.0786572144143</v>
+        <v>94.6945091970608</v>
       </c>
       <c r="D408">
-        <v>3.59802562257725</v>
+        <v>3.60721304220888</v>
       </c>
     </row>
     <row r="409">
@@ -5968,13 +5968,13 @@
         <v>2025-06</v>
       </c>
       <c r="B409">
-        <v>97.5843284125511</v>
+        <v>96.1236298550595</v>
       </c>
       <c r="C409">
-        <v>97.6493342268278</v>
+        <v>97.0713907585439</v>
       </c>
       <c r="D409">
-        <v>3.59204331718325</v>
+        <v>3.5611559978617</v>
       </c>
     </row>
     <row r="410">
@@ -5982,13 +5982,13 @@
         <v>2025-07</v>
       </c>
       <c r="B410">
-        <v>97.7493314758304</v>
+        <v>97.0217354767454</v>
       </c>
       <c r="C410">
-        <v>99.5047337395797</v>
+        <v>98.6553224645777</v>
       </c>
       <c r="D410">
-        <v>3.54147398646285</v>
+        <v>3.44343694154561</v>
       </c>
     </row>
     <row r="411">
@@ -5996,13 +5996,13 @@
         <v>2025-08</v>
       </c>
       <c r="B411">
-        <v>100.26222360823</v>
+        <v>99.0744527617291</v>
       </c>
       <c r="C411">
-        <v>101.761651917386</v>
+        <v>101.061995021637</v>
       </c>
       <c r="D411">
-        <v>3.39841040671804</v>
+        <v>3.35723249176385</v>
       </c>
     </row>
     <row r="412">
@@ -6010,13 +6010,13 @@
         <v>2025-09</v>
       </c>
       <c r="B412">
-        <v>100.484517701316</v>
+        <v>99.4132814374889</v>
       </c>
       <c r="C412">
-        <v>102.508351327483</v>
+        <v>101.712317574066</v>
       </c>
       <c r="D412">
-        <v>3.16375654354732</v>
+        <v>3.30215229542048</v>
       </c>
     </row>
     <row r="413">
@@ -6024,10 +6024,13 @@
         <v>2025-10</v>
       </c>
       <c r="B413">
-        <v>99.5075464689196</v>
+        <v>98.6340926761855</v>
       </c>
       <c r="C413">
-        <v>102.284184772845</v>
+        <v>101.423584962027</v>
+      </c>
+      <c r="D413">
+        <v>3.27784902104101</v>
       </c>
     </row>
     <row r="414">
@@ -6035,10 +6038,13 @@
         <v>2025-11</v>
       </c>
       <c r="B414">
-        <v>100.153246218352</v>
+        <v>99.1711032883936</v>
       </c>
       <c r="C414">
-        <v>99.859417872887</v>
+        <v>99.3193128955093</v>
+      </c>
+      <c r="D414">
+        <v>3.17486654434546</v>
       </c>
     </row>
     <row r="415">
@@ -6046,10 +6052,13 @@
         <v>2025-12</v>
       </c>
       <c r="B415">
-        <v>100.705577999516</v>
+        <v>100.102992927439</v>
       </c>
       <c r="C415">
-        <v>101.312174164088</v>
+        <v>100.702953586276</v>
+      </c>
+      <c r="D415">
+        <v>2.99383302903433</v>
       </c>
     </row>
     <row r="416">
@@ -6057,10 +6066,10 @@
         <v>2026-01</v>
       </c>
       <c r="B416">
-        <v>102.323038122206</v>
+        <v>101.525598865588</v>
       </c>
       <c r="C416">
-        <v>102.107953737322</v>
+        <v>101.128407220134</v>
       </c>
     </row>
     <row r="417">
@@ -6068,10 +6077,10 @@
         <v>2026-02</v>
       </c>
       <c r="B417">
-        <v>102.994330336713</v>
+        <v>101.76644134319</v>
       </c>
       <c r="C417">
-        <v>102.524912064093</v>
+        <v>101.680941507927</v>
       </c>
     </row>
     <row r="418">
@@ -6079,10 +6088,10 @@
         <v>2026-03</v>
       </c>
       <c r="B418">
-        <v>102.326151912722</v>
+        <v>101.68657607946</v>
       </c>
       <c r="C418">
-        <v>101.220702996584</v>
+        <v>100.773684334391</v>
       </c>
     </row>
     <row r="419">
@@ -6090,15 +6099,26 @@
         <v>2026-04</v>
       </c>
       <c r="B419">
-        <v>102.128859419195</v>
+        <v>101.635489418794</v>
       </c>
       <c r="C419">
-        <v>102.877278585314</v>
+        <v>101.734100676593</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>2026-05</v>
+      </c>
+      <c r="B420">
+        <v>103.545928788692</v>
+      </c>
+      <c r="C420">
+        <v>100.302062101049</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D419"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D420"/>
   </ignoredErrors>
 </worksheet>
 </file>